--- a/UT_Lab04,05,06/UT_Lab04,05,06.xlsx
+++ b/UT_Lab04,05,06/UT_Lab04,05,06.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11520" windowHeight="9000" firstSheet="1" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="8556" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="UT_Lab04" sheetId="4" r:id="rId1"/>
@@ -37,7 +37,7 @@
     <author>BAOHA</author>
   </authors>
   <commentList>
-    <comment ref="L3" authorId="0">
+    <comment ref="K3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="125">
   <si>
     <t>Function Code</t>
   </si>
@@ -431,10 +431,7 @@
     <t xml:space="preserve"> Assert.AreEqual failed. Expected:&lt;a&gt;. Actual:&lt;&gt;.</t>
   </si>
   <si>
-    <t>Sum(long s0, out long s)</t>
-  </si>
-  <si>
-    <t>Đỗ Minh Tuấn</t>
+    <t>BinToDec(String sbin)</t>
   </si>
   <si>
     <t>Lines  of code</t>
@@ -443,22 +440,13 @@
     <t>Tìm k bé nhất thoả mãn s = 1 + 2 + 3 + … + k &gt; s0, cho biết s khi đó có giá trị bao nhiêu</t>
   </si>
   <si>
-    <t>s0</t>
-  </si>
-  <si>
-    <t>k</t>
-  </si>
-  <si>
-    <t>Log message</t>
+    <t>sbin</t>
+  </si>
+  <si>
+    <t>102bfg</t>
   </si>
   <si>
     <t xml:space="preserve">Chú thích: </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Assert.AreEqual failed. Expected:&lt;1&gt;. Actual:&lt;2&gt;</t>
-  </si>
-  <si>
-    <t>Assert.AreEqual failed. Expected:&lt;6&gt;. Actual:&lt;4&gt;.</t>
   </si>
 </sst>
 </file>
@@ -472,7 +460,7 @@
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="mm/dd"/>
   </numFmts>
-  <fonts count="51">
+  <fonts count="48">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -519,12 +507,6 @@
       <b/>
       <sz val="10"/>
       <name val="Courier New"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
@@ -580,12 +562,6 @@
       <b/>
       <sz val="10"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Tahoma"/>
       <charset val="1"/>
     </font>
     <font>
@@ -604,11 +580,6 @@
     <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1051,7 +1022,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="56">
+  <borders count="53">
     <border>
       <left/>
       <right/>
@@ -1551,41 +1522,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -1758,145 +1694,145 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="45" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="48" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="46" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="46" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="47" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="49" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="48" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="49" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="49" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="50" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="48" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="50" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="11" borderId="51" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="51" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="52" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="52" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="12" borderId="51" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="13" borderId="53" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="54" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="55" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2090,14 +2026,8 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="36" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2123,33 +2053,25 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="38" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="41" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="37" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="42" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="43" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -2159,23 +2081,29 @@
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="45" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="42" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment textRotation="255"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="54" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="54" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="38" xfId="54" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="38" xfId="54" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2183,111 +2111,105 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="38" xfId="54" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="38" xfId="54" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="38" xfId="54" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="38" xfId="54" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="54" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="54" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="38" xfId="54" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="54" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="38" xfId="54" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="38" xfId="54" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="38" xfId="54" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="38" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="54" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="54" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="38" xfId="54" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="58" fontId="22" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="54" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="38" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" xfId="54" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" xfId="54" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="55">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2689,69 +2611,44 @@
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4933950" cy="1981835"/>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>990600</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>159385</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="3" name="Picture 2"/>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
+        <a:blip r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7589520" y="247650"/>
-          <a:ext cx="4933950" cy="1981835"/>
+          <a:off x="7353300" y="514350"/>
+          <a:ext cx="6324600" cy="2019300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3047,1495 +2944,1495 @@
   <dimension ref="A2:Z59"/>
   <sheetFormatPr defaultColWidth="7.66666666666667" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="15.4444444444444" style="104" customWidth="1"/>
-    <col min="2" max="2" width="9.66666666666667" style="104" customWidth="1"/>
-    <col min="3" max="3" width="12.1111111111111" style="104" customWidth="1"/>
-    <col min="4" max="4" width="16.2222222222222" style="104" customWidth="1"/>
-    <col min="5" max="17" width="3.33333333333333" style="104" customWidth="1"/>
-    <col min="18" max="18" width="2.66666666666667" style="104" customWidth="1"/>
-    <col min="19" max="19" width="8.88888888888889" style="104" customWidth="1"/>
-    <col min="20" max="20" width="23.4444444444444" style="104" customWidth="1"/>
-    <col min="21" max="21" width="13.3333333333333" style="104" customWidth="1"/>
-    <col min="22" max="22" width="12.4444444444444" style="104" customWidth="1"/>
-    <col min="23" max="23" width="14.1111111111111" style="104" customWidth="1"/>
-    <col min="24" max="24" width="19.1111111111111" style="104" customWidth="1"/>
-    <col min="25" max="25" width="28" style="104" customWidth="1"/>
-    <col min="26" max="26" width="8.77777777777778" style="104" customWidth="1"/>
-    <col min="27" max="16384" width="7.66666666666667" style="104"/>
+    <col min="1" max="1" width="15.4444444444444" style="98" customWidth="1"/>
+    <col min="2" max="2" width="9.66666666666667" style="98" customWidth="1"/>
+    <col min="3" max="3" width="12.1111111111111" style="98" customWidth="1"/>
+    <col min="4" max="4" width="16.2222222222222" style="98" customWidth="1"/>
+    <col min="5" max="17" width="3.33333333333333" style="98" customWidth="1"/>
+    <col min="18" max="18" width="2.66666666666667" style="98" customWidth="1"/>
+    <col min="19" max="19" width="8.88888888888889" style="98" customWidth="1"/>
+    <col min="20" max="20" width="23.4444444444444" style="98" customWidth="1"/>
+    <col min="21" max="21" width="13.3333333333333" style="98" customWidth="1"/>
+    <col min="22" max="22" width="12.4444444444444" style="98" customWidth="1"/>
+    <col min="23" max="23" width="14.1111111111111" style="98" customWidth="1"/>
+    <col min="24" max="24" width="19.1111111111111" style="98" customWidth="1"/>
+    <col min="25" max="25" width="28" style="98" customWidth="1"/>
+    <col min="26" max="26" width="8.77777777777778" style="98" customWidth="1"/>
+    <col min="27" max="16384" width="7.66666666666667" style="98"/>
   </cols>
   <sheetData>
-    <row r="2" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A2" s="105" t="s">
+    <row r="2" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A2" s="99" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="106"/>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="105" t="s">
+      <c r="B2" s="100"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="108" t="str">
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="102" t="str">
         <f>[1]FunctionList!D15</f>
         <v>HuyChuoi(String s, int n, int p)</v>
       </c>
-      <c r="M2" s="109"/>
-      <c r="N2" s="109"/>
-      <c r="O2" s="109"/>
-      <c r="P2" s="109"/>
-      <c r="Q2" s="109"/>
-    </row>
-    <row r="3" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A3" s="105" t="s">
+      <c r="M2" s="103"/>
+      <c r="N2" s="103"/>
+      <c r="O2" s="103"/>
+      <c r="P2" s="103"/>
+      <c r="Q2" s="103"/>
+    </row>
+    <row r="3" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A3" s="99" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="109" t="s">
+      <c r="B3" s="103" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="105" t="s">
+      <c r="C3" s="101"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="99" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="105"/>
-      <c r="G3" s="105"/>
-      <c r="H3" s="105"/>
-      <c r="I3" s="105"/>
-      <c r="J3" s="105"/>
-      <c r="K3" s="105"/>
-      <c r="L3" s="110" t="s">
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="99"/>
+      <c r="J3" s="99"/>
+      <c r="K3" s="99"/>
+      <c r="L3" s="104" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="110"/>
-      <c r="N3" s="110"/>
-      <c r="O3" s="110"/>
-      <c r="P3" s="110"/>
-      <c r="Q3" s="110"/>
-    </row>
-    <row r="4" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A4" s="105" t="s">
+      <c r="M3" s="104"/>
+      <c r="N3" s="104"/>
+      <c r="O3" s="104"/>
+      <c r="P3" s="104"/>
+      <c r="Q3" s="104"/>
+    </row>
+    <row r="4" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A4" s="99" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="109"/>
-      <c r="C4" s="109"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="105" t="s">
+      <c r="B4" s="103"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="105"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="105"/>
-      <c r="I4" s="105"/>
-      <c r="J4" s="105"/>
-      <c r="K4" s="105"/>
-      <c r="L4" s="109">
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="99"/>
+      <c r="K4" s="99"/>
+      <c r="L4" s="103">
         <v>0</v>
       </c>
-      <c r="M4" s="109"/>
-      <c r="N4" s="109"/>
-      <c r="O4" s="109"/>
-      <c r="P4" s="109"/>
-      <c r="Q4" s="109"/>
-    </row>
-    <row r="5" s="104" customFormat="1" ht="55" customHeight="1" spans="1:26">
-      <c r="A5" s="105" t="s">
+      <c r="M4" s="103"/>
+      <c r="N4" s="103"/>
+      <c r="O4" s="103"/>
+      <c r="P4" s="103"/>
+      <c r="Q4" s="103"/>
+    </row>
+    <row r="5" s="98" customFormat="1" ht="55" customHeight="1" spans="1:26">
+      <c r="A5" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="139" t="s">
+      <c r="B5" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="111"/>
-      <c r="D5" s="111"/>
-      <c r="E5" s="111"/>
-      <c r="F5" s="111"/>
-      <c r="G5" s="111"/>
-      <c r="H5" s="111"/>
-      <c r="I5" s="111"/>
-      <c r="J5" s="111"/>
-      <c r="K5" s="111"/>
-      <c r="L5" s="111"/>
-      <c r="M5" s="111"/>
-      <c r="N5" s="111"/>
-      <c r="O5" s="111"/>
-      <c r="P5" s="111"/>
-      <c r="Q5" s="111"/>
-    </row>
-    <row r="6" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A6" s="112" t="s">
+      <c r="C5" s="105"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="105"/>
+      <c r="J5" s="105"/>
+      <c r="K5" s="105"/>
+      <c r="L5" s="105"/>
+      <c r="M5" s="105"/>
+      <c r="N5" s="105"/>
+      <c r="O5" s="105"/>
+      <c r="P5" s="105"/>
+      <c r="Q5" s="105"/>
+    </row>
+    <row r="6" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A6" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="112" t="s">
+      <c r="B6" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="112"/>
-      <c r="D6" s="112"/>
-      <c r="E6" s="112" t="s">
+      <c r="C6" s="106"/>
+      <c r="D6" s="106"/>
+      <c r="E6" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="112"/>
-      <c r="G6" s="112"/>
-      <c r="H6" s="112"/>
-      <c r="I6" s="112" t="s">
+      <c r="F6" s="106"/>
+      <c r="G6" s="106"/>
+      <c r="H6" s="106"/>
+      <c r="I6" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="112"/>
-      <c r="K6" s="112"/>
-      <c r="L6" s="112" t="s">
+      <c r="J6" s="106"/>
+      <c r="K6" s="106"/>
+      <c r="L6" s="106" t="s">
         <v>13</v>
       </c>
-      <c r="M6" s="112"/>
-      <c r="N6" s="112"/>
-      <c r="O6" s="112"/>
-      <c r="P6" s="112"/>
-      <c r="Q6" s="112"/>
-    </row>
-    <row r="7" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A7" s="109">
+      <c r="M6" s="106"/>
+      <c r="N6" s="106"/>
+      <c r="O6" s="106"/>
+      <c r="P6" s="106"/>
+      <c r="Q6" s="106"/>
+    </row>
+    <row r="7" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A7" s="103">
         <f>COUNTIF(E42:Q42,"p")</f>
         <v>2</v>
       </c>
-      <c r="B7" s="109">
+      <c r="B7" s="103">
         <f>COUNTIF(E42:Q42,"f*")</f>
         <v>11</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="109">
+      <c r="C7" s="103"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="103">
         <f>L7-A7-B7</f>
         <v>0</v>
       </c>
-      <c r="F7" s="109"/>
-      <c r="G7" s="109"/>
-      <c r="H7" s="109"/>
-      <c r="I7" s="109">
+      <c r="F7" s="103"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="103">
         <f>COUNTIF(E41:Q41,"N")</f>
         <v>5</v>
       </c>
-      <c r="J7" s="109">
+      <c r="J7" s="103">
         <f>COUNTIF(E41:Q41,"A")</f>
         <v>0</v>
       </c>
-      <c r="K7" s="109">
+      <c r="K7" s="103">
         <f>COUNTIF(E41:Q41,"B")</f>
         <v>8</v>
       </c>
-      <c r="L7" s="109">
+      <c r="L7" s="103">
         <f>COUNTA(E41:Q41)</f>
         <v>13</v>
       </c>
-      <c r="M7" s="109"/>
-      <c r="N7" s="109"/>
-      <c r="O7" s="109"/>
-      <c r="P7" s="109"/>
-      <c r="Q7" s="109"/>
-    </row>
-    <row r="9" s="104" customFormat="1" ht="67.5" customHeight="1" spans="1:26">
-      <c r="A9" s="113"/>
-      <c r="B9" s="113"/>
-      <c r="C9" s="113"/>
-      <c r="D9" s="113"/>
-      <c r="E9" s="114" t="s">
+      <c r="M7" s="103"/>
+      <c r="N7" s="103"/>
+      <c r="O7" s="103"/>
+      <c r="P7" s="103"/>
+      <c r="Q7" s="103"/>
+    </row>
+    <row r="9" s="98" customFormat="1" ht="67.5" customHeight="1" spans="1:26">
+      <c r="A9" s="107"/>
+      <c r="B9" s="107"/>
+      <c r="C9" s="107"/>
+      <c r="D9" s="107"/>
+      <c r="E9" s="108" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="114" t="s">
+      <c r="F9" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="114" t="s">
+      <c r="G9" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="114" t="s">
+      <c r="H9" s="108" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="114" t="s">
+      <c r="I9" s="108" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="114" t="s">
+      <c r="J9" s="108" t="s">
         <v>19</v>
       </c>
-      <c r="K9" s="114" t="s">
+      <c r="K9" s="108" t="s">
         <v>20</v>
       </c>
-      <c r="L9" s="114" t="s">
+      <c r="L9" s="108" t="s">
         <v>21</v>
       </c>
-      <c r="M9" s="114" t="s">
+      <c r="M9" s="108" t="s">
         <v>22</v>
       </c>
-      <c r="N9" s="114" t="s">
+      <c r="N9" s="108" t="s">
         <v>23</v>
       </c>
-      <c r="O9" s="114" t="s">
+      <c r="O9" s="108" t="s">
         <v>24</v>
       </c>
-      <c r="P9" s="114" t="s">
+      <c r="P9" s="108" t="s">
         <v>25</v>
       </c>
-      <c r="Q9" s="114" t="s">
+      <c r="Q9" s="108" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A10" s="115" t="s">
+    <row r="10" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A10" s="109" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="105" t="s">
+      <c r="B10" s="99" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="105"/>
-      <c r="D10" s="105"/>
-      <c r="E10" s="116"/>
-      <c r="F10" s="116"/>
-      <c r="G10" s="116"/>
-      <c r="H10" s="116"/>
-      <c r="I10" s="116"/>
-      <c r="J10" s="116"/>
-      <c r="K10" s="116"/>
-      <c r="L10" s="116"/>
-      <c r="M10" s="116"/>
-      <c r="N10" s="116"/>
-      <c r="O10" s="116"/>
-      <c r="P10" s="116"/>
-      <c r="Q10" s="116"/>
-    </row>
-    <row r="11" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A11" s="115"/>
-      <c r="B11" s="117" t="s">
+      <c r="C10" s="99"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="110"/>
+      <c r="F10" s="110"/>
+      <c r="G10" s="110"/>
+      <c r="H10" s="110"/>
+      <c r="I10" s="110"/>
+      <c r="J10" s="110"/>
+      <c r="K10" s="110"/>
+      <c r="L10" s="110"/>
+      <c r="M10" s="110"/>
+      <c r="N10" s="110"/>
+      <c r="O10" s="110"/>
+      <c r="P10" s="110"/>
+      <c r="Q10" s="110"/>
+    </row>
+    <row r="11" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A11" s="109"/>
+      <c r="B11" s="111" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="117"/>
-      <c r="D11" s="117"/>
-      <c r="E11" s="118" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" s="118" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" s="118" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="118" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" s="118" t="s">
-        <v>30</v>
-      </c>
-      <c r="J11" s="118"/>
-      <c r="K11" s="118" t="s">
-        <v>30</v>
-      </c>
-      <c r="L11" s="118" t="s">
-        <v>30</v>
-      </c>
-      <c r="M11" s="118" t="s">
-        <v>30</v>
-      </c>
-      <c r="N11" s="118" t="s">
-        <v>30</v>
-      </c>
-      <c r="O11" s="140" t="s">
-        <v>30</v>
-      </c>
-      <c r="P11" s="140" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q11" s="118" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A12" s="115"/>
-      <c r="B12" s="117" t="s">
+      <c r="C11" s="111"/>
+      <c r="D11" s="111"/>
+      <c r="E11" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11" s="112"/>
+      <c r="K11" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="L11" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="M11" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="N11" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="O11" s="134" t="s">
+        <v>30</v>
+      </c>
+      <c r="P11" s="134" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q11" s="112" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A12" s="109"/>
+      <c r="B12" s="111" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="117"/>
-      <c r="D12" s="117"/>
-      <c r="E12" s="116"/>
-      <c r="F12" s="116"/>
-      <c r="G12" s="116"/>
-      <c r="H12" s="140"/>
-      <c r="I12" s="140"/>
-      <c r="J12" s="140" t="s">
-        <v>30</v>
-      </c>
-      <c r="K12" s="140"/>
-      <c r="L12" s="140"/>
-      <c r="M12" s="140"/>
-      <c r="N12" s="140"/>
-      <c r="O12" s="118"/>
-      <c r="P12" s="140"/>
-      <c r="Q12" s="140"/>
-    </row>
-    <row r="13" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A13" s="115"/>
-      <c r="B13" s="105" t="s">
+      <c r="C12" s="111"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="110"/>
+      <c r="F12" s="110"/>
+      <c r="G12" s="110"/>
+      <c r="H12" s="134"/>
+      <c r="I12" s="134"/>
+      <c r="J12" s="134" t="s">
+        <v>30</v>
+      </c>
+      <c r="K12" s="134"/>
+      <c r="L12" s="134"/>
+      <c r="M12" s="134"/>
+      <c r="N12" s="134"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="134"/>
+      <c r="Q12" s="134"/>
+    </row>
+    <row r="13" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A13" s="109"/>
+      <c r="B13" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="105"/>
-      <c r="D13" s="105"/>
-      <c r="E13" s="116"/>
-      <c r="F13" s="116"/>
-      <c r="G13" s="116"/>
-      <c r="H13" s="140"/>
-      <c r="I13" s="140"/>
-      <c r="J13" s="140"/>
-      <c r="K13" s="140"/>
-      <c r="L13" s="140"/>
-      <c r="M13" s="140"/>
-      <c r="N13" s="140"/>
-      <c r="O13" s="140"/>
-      <c r="P13" s="140"/>
-      <c r="Q13" s="140"/>
-    </row>
-    <row r="14" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A14" s="115"/>
-      <c r="B14" s="117">
+      <c r="C13" s="99"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="110"/>
+      <c r="F13" s="110"/>
+      <c r="G13" s="110"/>
+      <c r="H13" s="134"/>
+      <c r="I13" s="134"/>
+      <c r="J13" s="134"/>
+      <c r="K13" s="134"/>
+      <c r="L13" s="134"/>
+      <c r="M13" s="134"/>
+      <c r="N13" s="134"/>
+      <c r="O13" s="134"/>
+      <c r="P13" s="134"/>
+      <c r="Q13" s="134"/>
+    </row>
+    <row r="14" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A14" s="109"/>
+      <c r="B14" s="111">
         <v>3</v>
       </c>
-      <c r="C14" s="117"/>
-      <c r="D14" s="117"/>
-      <c r="E14" s="118" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="G14" s="118" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14" s="118"/>
-      <c r="I14" s="140"/>
-      <c r="J14" s="118"/>
-      <c r="K14" s="140"/>
-      <c r="L14" s="140"/>
-      <c r="M14" s="116"/>
-      <c r="N14" s="116"/>
-      <c r="O14" s="116"/>
-      <c r="P14" s="116"/>
-      <c r="Q14" s="118"/>
-      <c r="S14" s="126"/>
-      <c r="T14" s="126"/>
-      <c r="U14" s="126"/>
-      <c r="V14" s="126"/>
-      <c r="W14" s="126"/>
-      <c r="X14" s="126"/>
-      <c r="Y14" s="126"/>
-      <c r="Z14" s="126"/>
-    </row>
-    <row r="15" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A15" s="115"/>
-      <c r="B15" s="117">
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="112"/>
+      <c r="I14" s="134"/>
+      <c r="J14" s="112"/>
+      <c r="K14" s="134"/>
+      <c r="L14" s="134"/>
+      <c r="M14" s="110"/>
+      <c r="N14" s="110"/>
+      <c r="O14" s="110"/>
+      <c r="P14" s="110"/>
+      <c r="Q14" s="112"/>
+      <c r="S14" s="120"/>
+      <c r="T14" s="120"/>
+      <c r="U14" s="120"/>
+      <c r="V14" s="120"/>
+      <c r="W14" s="120"/>
+      <c r="X14" s="120"/>
+      <c r="Y14" s="120"/>
+      <c r="Z14" s="120"/>
+    </row>
+    <row r="15" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A15" s="109"/>
+      <c r="B15" s="111">
         <v>-2</v>
       </c>
-      <c r="C15" s="117"/>
-      <c r="D15" s="117"/>
-      <c r="E15" s="116"/>
-      <c r="F15" s="118"/>
-      <c r="G15" s="140"/>
-      <c r="H15" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="140"/>
-      <c r="J15" s="140"/>
-      <c r="K15" s="140"/>
-      <c r="L15" s="116"/>
-      <c r="M15" s="116"/>
-      <c r="N15" s="116"/>
-      <c r="O15" s="116"/>
-      <c r="P15" s="116"/>
-      <c r="Q15" s="116"/>
-    </row>
-    <row r="16" s="104" customFormat="1" ht="15" customHeight="1" spans="1:26">
-      <c r="A16" s="115"/>
-      <c r="B16" s="117">
+      <c r="C15" s="111"/>
+      <c r="D15" s="111"/>
+      <c r="E15" s="110"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="134"/>
+      <c r="H15" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="134"/>
+      <c r="J15" s="134"/>
+      <c r="K15" s="134"/>
+      <c r="L15" s="110"/>
+      <c r="M15" s="110"/>
+      <c r="N15" s="110"/>
+      <c r="O15" s="110"/>
+      <c r="P15" s="110"/>
+      <c r="Q15" s="110"/>
+    </row>
+    <row r="16" s="98" customFormat="1" ht="15" customHeight="1" spans="1:26">
+      <c r="A16" s="109"/>
+      <c r="B16" s="111">
         <v>5</v>
       </c>
-      <c r="C16" s="117"/>
-      <c r="D16" s="117"/>
-      <c r="E16" s="116"/>
-      <c r="F16" s="140"/>
-      <c r="G16" s="140"/>
-      <c r="H16" s="140"/>
-      <c r="I16" s="118" t="s">
-        <v>30</v>
-      </c>
-      <c r="J16" s="140"/>
-      <c r="K16" s="140"/>
-      <c r="L16" s="116"/>
-      <c r="M16" s="116"/>
-      <c r="N16" s="116"/>
-      <c r="O16" s="116"/>
-      <c r="P16" s="116"/>
-      <c r="Q16" s="116"/>
-      <c r="T16" s="141" t="s">
+      <c r="C16" s="111"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="110"/>
+      <c r="F16" s="134"/>
+      <c r="G16" s="134"/>
+      <c r="H16" s="134"/>
+      <c r="I16" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="J16" s="134"/>
+      <c r="K16" s="134"/>
+      <c r="L16" s="110"/>
+      <c r="M16" s="110"/>
+      <c r="N16" s="110"/>
+      <c r="O16" s="110"/>
+      <c r="P16" s="110"/>
+      <c r="Q16" s="110"/>
+      <c r="T16" s="135" t="s">
         <v>27</v>
       </c>
-      <c r="U16" s="142" t="s">
+      <c r="U16" s="136" t="s">
         <v>33</v>
       </c>
-      <c r="V16" s="143" t="s">
+      <c r="V16" s="137" t="s">
         <v>34</v>
       </c>
-      <c r="W16" s="142" t="s">
+      <c r="W16" s="136" t="s">
         <v>35</v>
       </c>
-      <c r="X16" s="142" t="s">
+      <c r="X16" s="136" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A17" s="115"/>
-      <c r="B17" s="117">
+    <row r="17" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A17" s="109"/>
+      <c r="B17" s="111">
         <v>0</v>
       </c>
-      <c r="C17" s="117"/>
-      <c r="D17" s="117"/>
-      <c r="E17" s="116"/>
-      <c r="F17" s="140"/>
-      <c r="G17" s="140"/>
-      <c r="H17" s="140"/>
-      <c r="I17" s="140"/>
-      <c r="J17" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="K17" s="118" t="s">
-        <v>30</v>
-      </c>
-      <c r="L17" s="116"/>
-      <c r="M17" s="116"/>
-      <c r="N17" s="116"/>
-      <c r="O17" s="118"/>
-      <c r="P17" s="116"/>
-      <c r="Q17" s="116"/>
-      <c r="S17" s="127"/>
-      <c r="T17" s="144" t="s">
+      <c r="C17" s="111"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="110"/>
+      <c r="F17" s="134"/>
+      <c r="G17" s="134"/>
+      <c r="H17" s="134"/>
+      <c r="I17" s="134"/>
+      <c r="J17" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="K17" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="L17" s="110"/>
+      <c r="M17" s="110"/>
+      <c r="N17" s="110"/>
+      <c r="O17" s="112"/>
+      <c r="P17" s="110"/>
+      <c r="Q17" s="110"/>
+      <c r="S17" s="121"/>
+      <c r="T17" s="138" t="s">
         <v>28</v>
       </c>
-      <c r="U17" s="144" t="s">
+      <c r="U17" s="138" t="s">
         <v>37</v>
       </c>
-      <c r="V17" s="144" t="s">
+      <c r="V17" s="138" t="s">
         <v>38</v>
       </c>
-      <c r="W17" s="144" t="s">
+      <c r="W17" s="138" t="s">
         <v>39</v>
       </c>
-      <c r="X17" s="144" t="s">
+      <c r="X17" s="138" t="s">
         <v>40</v>
       </c>
-      <c r="Y17" s="127"/>
-      <c r="Z17" s="127"/>
-    </row>
-    <row r="18" s="104" customFormat="1" ht="15" customHeight="1" spans="1:26">
-      <c r="A18" s="115"/>
-      <c r="B18" s="123">
+      <c r="Y17" s="121"/>
+      <c r="Z17" s="121"/>
+    </row>
+    <row r="18" s="98" customFormat="1" ht="15" customHeight="1" spans="1:26">
+      <c r="A18" s="109"/>
+      <c r="B18" s="117">
         <v>1</v>
       </c>
-      <c r="C18" s="124"/>
-      <c r="D18" s="125"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="116"/>
-      <c r="H18" s="116"/>
-      <c r="I18" s="116"/>
-      <c r="J18" s="116"/>
-      <c r="K18" s="116"/>
-      <c r="L18" s="118" t="s">
-        <v>30</v>
-      </c>
-      <c r="M18" s="116"/>
-      <c r="N18" s="116"/>
-      <c r="O18" s="116"/>
-      <c r="P18" s="118"/>
-      <c r="Q18" s="116"/>
-      <c r="S18" s="127"/>
-      <c r="T18" s="145" t="s">
+      <c r="C18" s="118"/>
+      <c r="D18" s="119"/>
+      <c r="E18" s="110"/>
+      <c r="F18" s="110"/>
+      <c r="G18" s="110"/>
+      <c r="H18" s="110"/>
+      <c r="I18" s="110"/>
+      <c r="J18" s="110"/>
+      <c r="K18" s="110"/>
+      <c r="L18" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="M18" s="110"/>
+      <c r="N18" s="110"/>
+      <c r="O18" s="110"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="110"/>
+      <c r="S18" s="121"/>
+      <c r="T18" s="139" t="s">
         <v>41</v>
       </c>
-      <c r="U18" s="144" t="s">
+      <c r="U18" s="138" t="s">
         <v>42</v>
       </c>
-      <c r="V18" s="144" t="s">
+      <c r="V18" s="138" t="s">
         <v>43</v>
       </c>
-      <c r="W18" s="144">
+      <c r="W18" s="138">
         <v>0</v>
       </c>
-      <c r="X18" s="144">
+      <c r="X18" s="138">
         <v>-1</v>
       </c>
-      <c r="Y18" s="127"/>
-      <c r="Z18" s="127"/>
-    </row>
-    <row r="19" s="104" customFormat="1" ht="15" customHeight="1" spans="1:26">
-      <c r="A19" s="115"/>
-      <c r="B19" s="123">
+      <c r="Y18" s="121"/>
+      <c r="Z18" s="121"/>
+    </row>
+    <row r="19" s="98" customFormat="1" ht="15" customHeight="1" spans="1:26">
+      <c r="A19" s="109"/>
+      <c r="B19" s="117">
         <v>4</v>
       </c>
-      <c r="C19" s="124"/>
-      <c r="D19" s="125"/>
-      <c r="E19" s="116"/>
-      <c r="F19" s="116"/>
-      <c r="G19" s="116"/>
-      <c r="H19" s="116"/>
-      <c r="I19" s="116"/>
-      <c r="J19" s="116"/>
-      <c r="K19" s="116"/>
-      <c r="L19" s="118"/>
-      <c r="M19" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="N19" s="119"/>
-      <c r="O19" s="119"/>
-      <c r="P19" s="118"/>
-      <c r="Q19" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="S19" s="127"/>
-      <c r="T19" s="145"/>
-      <c r="U19" s="144"/>
-      <c r="V19" s="144"/>
-      <c r="W19" s="144"/>
-      <c r="X19" s="144"/>
-      <c r="Y19" s="127"/>
-      <c r="Z19" s="127"/>
-    </row>
-    <row r="20" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A20" s="115"/>
-      <c r="B20" s="117">
+      <c r="C19" s="118"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="110"/>
+      <c r="F19" s="110"/>
+      <c r="G19" s="110"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="110"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="110"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="N19" s="113"/>
+      <c r="O19" s="113"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="S19" s="121"/>
+      <c r="T19" s="139"/>
+      <c r="U19" s="138"/>
+      <c r="V19" s="138"/>
+      <c r="W19" s="138"/>
+      <c r="X19" s="138"/>
+      <c r="Y19" s="121"/>
+      <c r="Z19" s="121"/>
+    </row>
+    <row r="20" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A20" s="109"/>
+      <c r="B20" s="111">
         <v>2</v>
       </c>
-      <c r="C20" s="117"/>
-      <c r="D20" s="117"/>
-      <c r="E20" s="116"/>
-      <c r="F20" s="116"/>
-      <c r="G20" s="116"/>
-      <c r="H20" s="116"/>
-      <c r="I20" s="116"/>
-      <c r="J20" s="116"/>
-      <c r="K20" s="116"/>
-      <c r="L20" s="116"/>
-      <c r="M20" s="118"/>
-      <c r="N20" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="O20" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="P20" s="119"/>
-      <c r="Q20" s="119"/>
-      <c r="S20" s="127"/>
-      <c r="T20" s="145"/>
-      <c r="U20" s="144"/>
-      <c r="V20" s="144" t="s">
+      <c r="C20" s="111"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="110"/>
+      <c r="F20" s="110"/>
+      <c r="G20" s="110"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="110"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="110"/>
+      <c r="L20" s="110"/>
+      <c r="M20" s="112"/>
+      <c r="N20" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="O20" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="P20" s="113"/>
+      <c r="Q20" s="113"/>
+      <c r="S20" s="121"/>
+      <c r="T20" s="139"/>
+      <c r="U20" s="138"/>
+      <c r="V20" s="138" t="s">
         <v>44</v>
       </c>
-      <c r="W20" s="144" t="s">
+      <c r="W20" s="138" t="s">
         <v>45</v>
       </c>
-      <c r="X20" s="144" t="s">
+      <c r="X20" s="138" t="s">
         <v>28</v>
       </c>
-      <c r="Y20" s="127"/>
-      <c r="Z20" s="127"/>
-    </row>
-    <row r="21" s="104" customFormat="1" ht="15" customHeight="1" spans="1:26">
-      <c r="A21" s="115"/>
-      <c r="B21" s="117">
+      <c r="Y20" s="121"/>
+      <c r="Z20" s="121"/>
+    </row>
+    <row r="21" s="98" customFormat="1" ht="15" customHeight="1" spans="1:26">
+      <c r="A21" s="109"/>
+      <c r="B21" s="111">
         <v>-1</v>
       </c>
-      <c r="C21" s="117"/>
-      <c r="D21" s="117"/>
-      <c r="E21" s="116"/>
-      <c r="F21" s="116"/>
-      <c r="G21" s="116"/>
-      <c r="H21" s="116"/>
-      <c r="I21" s="116"/>
-      <c r="J21" s="116"/>
-      <c r="K21" s="116"/>
-      <c r="L21" s="116"/>
-      <c r="M21" s="119"/>
-      <c r="N21" s="119"/>
-      <c r="O21" s="119"/>
-      <c r="P21" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q21" s="119"/>
-      <c r="S21" s="127"/>
-      <c r="T21" s="145"/>
-      <c r="U21" s="144"/>
-      <c r="V21" s="144" t="s">
+      <c r="C21" s="111"/>
+      <c r="D21" s="111"/>
+      <c r="E21" s="110"/>
+      <c r="F21" s="110"/>
+      <c r="G21" s="110"/>
+      <c r="H21" s="110"/>
+      <c r="I21" s="110"/>
+      <c r="J21" s="110"/>
+      <c r="K21" s="110"/>
+      <c r="L21" s="110"/>
+      <c r="M21" s="113"/>
+      <c r="N21" s="113"/>
+      <c r="O21" s="113"/>
+      <c r="P21" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q21" s="113"/>
+      <c r="S21" s="121"/>
+      <c r="T21" s="139"/>
+      <c r="U21" s="138"/>
+      <c r="V21" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="W21" s="144" t="s">
+      <c r="W21" s="138" t="s">
         <v>47</v>
       </c>
-      <c r="X21" s="144" t="s">
+      <c r="X21" s="138" t="s">
         <v>48</v>
       </c>
-      <c r="Y21" s="127"/>
-      <c r="Z21" s="127"/>
-    </row>
-    <row r="22" s="104" customFormat="1" ht="15" customHeight="1" spans="1:26">
-      <c r="A22" s="115"/>
-      <c r="B22" s="117"/>
-      <c r="C22" s="117"/>
-      <c r="D22" s="117"/>
-      <c r="E22" s="116"/>
-      <c r="F22" s="116"/>
-      <c r="G22" s="116"/>
-      <c r="H22" s="116"/>
-      <c r="I22" s="116"/>
-      <c r="J22" s="116"/>
-      <c r="K22" s="116"/>
-      <c r="L22" s="116"/>
-      <c r="M22" s="116"/>
-      <c r="N22" s="116"/>
-      <c r="O22" s="116"/>
-      <c r="P22" s="116"/>
-      <c r="Q22" s="116"/>
-      <c r="S22" s="127"/>
-      <c r="T22" s="145"/>
-      <c r="U22" s="144"/>
-      <c r="V22" s="144" t="s">
+      <c r="Y21" s="121"/>
+      <c r="Z21" s="121"/>
+    </row>
+    <row r="22" s="98" customFormat="1" ht="15" customHeight="1" spans="1:26">
+      <c r="A22" s="109"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="111"/>
+      <c r="D22" s="111"/>
+      <c r="E22" s="110"/>
+      <c r="F22" s="110"/>
+      <c r="G22" s="110"/>
+      <c r="H22" s="110"/>
+      <c r="I22" s="110"/>
+      <c r="J22" s="110"/>
+      <c r="K22" s="110"/>
+      <c r="L22" s="110"/>
+      <c r="M22" s="110"/>
+      <c r="N22" s="110"/>
+      <c r="O22" s="110"/>
+      <c r="P22" s="110"/>
+      <c r="Q22" s="110"/>
+      <c r="S22" s="121"/>
+      <c r="T22" s="139"/>
+      <c r="U22" s="138"/>
+      <c r="V22" s="138" t="s">
         <v>49</v>
       </c>
-      <c r="W22" s="144"/>
-      <c r="X22" s="144"/>
-      <c r="Y22" s="127"/>
-      <c r="Z22" s="127"/>
-    </row>
-    <row r="23" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A23" s="115"/>
-      <c r="B23" s="105" t="s">
+      <c r="W22" s="138"/>
+      <c r="X22" s="138"/>
+      <c r="Y22" s="121"/>
+      <c r="Z22" s="121"/>
+    </row>
+    <row r="23" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A23" s="109"/>
+      <c r="B23" s="99" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="105"/>
-      <c r="D23" s="105"/>
-      <c r="E23" s="118"/>
-      <c r="F23" s="118"/>
-      <c r="G23" s="116"/>
-      <c r="H23" s="116"/>
-      <c r="I23" s="118"/>
-      <c r="J23" s="116"/>
-      <c r="K23" s="116"/>
-      <c r="L23" s="118"/>
-      <c r="M23" s="118"/>
-      <c r="N23" s="118"/>
-      <c r="O23" s="116"/>
-      <c r="P23" s="116"/>
-      <c r="Q23" s="116"/>
-      <c r="S23" s="127"/>
-      <c r="T23" s="127"/>
-      <c r="U23" s="127"/>
-      <c r="V23" s="127"/>
-      <c r="W23" s="127"/>
-      <c r="X23" s="127"/>
-      <c r="Y23" s="127"/>
-      <c r="Z23" s="127"/>
-    </row>
-    <row r="24" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A24" s="115"/>
-      <c r="B24" s="117">
+      <c r="C23" s="99"/>
+      <c r="D23" s="99"/>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="110"/>
+      <c r="H23" s="110"/>
+      <c r="I23" s="112"/>
+      <c r="J23" s="110"/>
+      <c r="K23" s="110"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="110"/>
+      <c r="P23" s="110"/>
+      <c r="Q23" s="110"/>
+      <c r="S23" s="121"/>
+      <c r="T23" s="121"/>
+      <c r="U23" s="121"/>
+      <c r="V23" s="121"/>
+      <c r="W23" s="121"/>
+      <c r="X23" s="121"/>
+      <c r="Y23" s="121"/>
+      <c r="Z23" s="121"/>
+    </row>
+    <row r="24" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A24" s="109"/>
+      <c r="B24" s="111">
         <v>1</v>
       </c>
-      <c r="C24" s="117"/>
-      <c r="D24" s="117"/>
-      <c r="E24" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="F24" s="119"/>
-      <c r="G24" s="118"/>
-      <c r="H24" s="119"/>
-      <c r="I24" s="119"/>
-      <c r="J24" s="119"/>
-      <c r="K24" s="119"/>
-      <c r="L24" s="119"/>
-      <c r="M24" s="119"/>
-      <c r="N24" s="119"/>
-      <c r="O24" s="119"/>
-      <c r="P24" s="119"/>
-      <c r="Q24" s="119"/>
-      <c r="S24" s="127"/>
-      <c r="T24" s="127"/>
-      <c r="U24" s="127"/>
-      <c r="V24" s="127"/>
-      <c r="W24" s="127"/>
-      <c r="X24" s="127"/>
-      <c r="Y24" s="127"/>
-      <c r="Z24" s="127"/>
-    </row>
-    <row r="25" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A25" s="115"/>
-      <c r="B25" s="117">
+      <c r="C24" s="111"/>
+      <c r="D24" s="111"/>
+      <c r="E24" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="F24" s="113"/>
+      <c r="G24" s="112"/>
+      <c r="H24" s="113"/>
+      <c r="I24" s="113"/>
+      <c r="J24" s="113"/>
+      <c r="K24" s="113"/>
+      <c r="L24" s="113"/>
+      <c r="M24" s="113"/>
+      <c r="N24" s="113"/>
+      <c r="O24" s="113"/>
+      <c r="P24" s="113"/>
+      <c r="Q24" s="113"/>
+      <c r="S24" s="121"/>
+      <c r="T24" s="121"/>
+      <c r="U24" s="121"/>
+      <c r="V24" s="121"/>
+      <c r="W24" s="121"/>
+      <c r="X24" s="121"/>
+      <c r="Y24" s="121"/>
+      <c r="Z24" s="121"/>
+    </row>
+    <row r="25" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A25" s="109"/>
+      <c r="B25" s="111">
         <v>-2</v>
       </c>
-      <c r="C25" s="117"/>
-      <c r="D25" s="117"/>
-      <c r="E25" s="119"/>
-      <c r="F25" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="G25" s="119"/>
-      <c r="H25" s="118"/>
-      <c r="I25" s="119"/>
-      <c r="J25" s="119"/>
-      <c r="K25" s="119"/>
-      <c r="L25" s="119"/>
-      <c r="M25" s="119"/>
-      <c r="N25" s="119"/>
-      <c r="O25" s="119"/>
-      <c r="P25" s="119"/>
-      <c r="Q25" s="119"/>
-      <c r="S25" s="127"/>
-      <c r="T25" s="127"/>
-      <c r="U25" s="127"/>
-      <c r="V25" s="127"/>
-      <c r="W25" s="127"/>
-      <c r="X25" s="127"/>
-      <c r="Y25" s="127"/>
-      <c r="Z25" s="127"/>
-    </row>
-    <row r="26" s="104" customFormat="1" ht="15" customHeight="1" spans="1:26">
-      <c r="A26" s="115"/>
-      <c r="B26" s="117">
+      <c r="C25" s="111"/>
+      <c r="D25" s="111"/>
+      <c r="E25" s="113"/>
+      <c r="F25" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="G25" s="113"/>
+      <c r="H25" s="112"/>
+      <c r="I25" s="113"/>
+      <c r="J25" s="113"/>
+      <c r="K25" s="113"/>
+      <c r="L25" s="113"/>
+      <c r="M25" s="113"/>
+      <c r="N25" s="113"/>
+      <c r="O25" s="113"/>
+      <c r="P25" s="113"/>
+      <c r="Q25" s="113"/>
+      <c r="S25" s="121"/>
+      <c r="T25" s="121"/>
+      <c r="U25" s="121"/>
+      <c r="V25" s="121"/>
+      <c r="W25" s="121"/>
+      <c r="X25" s="121"/>
+      <c r="Y25" s="121"/>
+      <c r="Z25" s="121"/>
+    </row>
+    <row r="26" s="98" customFormat="1" ht="15" customHeight="1" spans="1:26">
+      <c r="A26" s="109"/>
+      <c r="B26" s="111">
         <v>7</v>
       </c>
-      <c r="C26" s="117"/>
-      <c r="D26" s="117"/>
-      <c r="E26" s="119"/>
-      <c r="F26" s="119"/>
-      <c r="G26" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="H26" s="119"/>
-      <c r="I26" s="119"/>
-      <c r="J26" s="118"/>
-      <c r="K26" s="119"/>
-      <c r="L26" s="119"/>
-      <c r="M26" s="119"/>
-      <c r="N26" s="119"/>
-      <c r="O26" s="118"/>
-      <c r="P26" s="118"/>
-      <c r="Q26" s="119"/>
-      <c r="S26" s="127"/>
-      <c r="T26" s="127"/>
-      <c r="U26" s="127"/>
-      <c r="V26" s="127"/>
-      <c r="W26" s="127"/>
-      <c r="X26" s="127"/>
-      <c r="Y26" s="127"/>
-      <c r="Z26" s="127"/>
-    </row>
-    <row r="27" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A27" s="115"/>
-      <c r="B27" s="117">
+      <c r="C26" s="111"/>
+      <c r="D26" s="111"/>
+      <c r="E26" s="113"/>
+      <c r="F26" s="113"/>
+      <c r="G26" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="H26" s="113"/>
+      <c r="I26" s="113"/>
+      <c r="J26" s="112"/>
+      <c r="K26" s="113"/>
+      <c r="L26" s="113"/>
+      <c r="M26" s="113"/>
+      <c r="N26" s="113"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="112"/>
+      <c r="Q26" s="113"/>
+      <c r="S26" s="121"/>
+      <c r="T26" s="121"/>
+      <c r="U26" s="121"/>
+      <c r="V26" s="121"/>
+      <c r="W26" s="121"/>
+      <c r="X26" s="121"/>
+      <c r="Y26" s="121"/>
+      <c r="Z26" s="121"/>
+    </row>
+    <row r="27" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A27" s="109"/>
+      <c r="B27" s="111">
         <v>4</v>
       </c>
-      <c r="C27" s="117"/>
-      <c r="D27" s="117"/>
-      <c r="E27" s="119"/>
-      <c r="F27" s="119"/>
-      <c r="G27" s="119"/>
-      <c r="H27" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="I27" s="119"/>
-      <c r="J27" s="119"/>
-      <c r="K27" s="118"/>
-      <c r="L27" s="119"/>
-      <c r="M27" s="119"/>
-      <c r="N27" s="119"/>
-      <c r="O27" s="119"/>
-      <c r="P27" s="119"/>
-      <c r="Q27" s="119"/>
-      <c r="S27" s="127"/>
-      <c r="T27" s="127"/>
-      <c r="U27" s="127"/>
-      <c r="V27" s="127"/>
-      <c r="W27" s="127"/>
-      <c r="X27" s="127"/>
-      <c r="Y27" s="127"/>
-      <c r="Z27" s="127"/>
-    </row>
-    <row r="28" s="104" customFormat="1" ht="15" customHeight="1" spans="1:26">
-      <c r="A28" s="115"/>
-      <c r="B28" s="117">
+      <c r="C27" s="111"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="113"/>
+      <c r="F27" s="113"/>
+      <c r="G27" s="113"/>
+      <c r="H27" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="I27" s="113"/>
+      <c r="J27" s="113"/>
+      <c r="K27" s="112"/>
+      <c r="L27" s="113"/>
+      <c r="M27" s="113"/>
+      <c r="N27" s="113"/>
+      <c r="O27" s="113"/>
+      <c r="P27" s="113"/>
+      <c r="Q27" s="113"/>
+      <c r="S27" s="121"/>
+      <c r="T27" s="121"/>
+      <c r="U27" s="121"/>
+      <c r="V27" s="121"/>
+      <c r="W27" s="121"/>
+      <c r="X27" s="121"/>
+      <c r="Y27" s="121"/>
+      <c r="Z27" s="121"/>
+    </row>
+    <row r="28" s="98" customFormat="1" ht="15" customHeight="1" spans="1:26">
+      <c r="A28" s="109"/>
+      <c r="B28" s="111">
         <v>2</v>
       </c>
-      <c r="C28" s="117"/>
-      <c r="D28" s="117"/>
-      <c r="E28" s="119"/>
-      <c r="F28" s="119"/>
-      <c r="G28" s="119"/>
-      <c r="H28" s="119"/>
-      <c r="I28" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="J28" s="119"/>
-      <c r="K28" s="119"/>
-      <c r="L28" s="119"/>
-      <c r="M28" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="N28" s="119"/>
-      <c r="O28" s="119"/>
-      <c r="P28" s="119"/>
-      <c r="Q28" s="118"/>
-      <c r="S28" s="127"/>
-      <c r="T28" s="127"/>
-      <c r="U28" s="127"/>
-      <c r="V28" s="127"/>
-      <c r="W28" s="127"/>
-      <c r="X28" s="127"/>
-      <c r="Y28" s="127"/>
-      <c r="Z28" s="127"/>
-    </row>
-    <row r="29" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A29" s="115"/>
-      <c r="B29" s="117">
+      <c r="C28" s="111"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="113"/>
+      <c r="F28" s="113"/>
+      <c r="G28" s="113"/>
+      <c r="H28" s="113"/>
+      <c r="I28" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="J28" s="113"/>
+      <c r="K28" s="113"/>
+      <c r="L28" s="113"/>
+      <c r="M28" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="N28" s="113"/>
+      <c r="O28" s="113"/>
+      <c r="P28" s="113"/>
+      <c r="Q28" s="112"/>
+      <c r="S28" s="121"/>
+      <c r="T28" s="121"/>
+      <c r="U28" s="121"/>
+      <c r="V28" s="121"/>
+      <c r="W28" s="121"/>
+      <c r="X28" s="121"/>
+      <c r="Y28" s="121"/>
+      <c r="Z28" s="121"/>
+    </row>
+    <row r="29" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A29" s="109"/>
+      <c r="B29" s="111">
         <v>0</v>
       </c>
-      <c r="C29" s="117"/>
-      <c r="D29" s="117"/>
-      <c r="E29" s="119"/>
-      <c r="F29" s="119"/>
-      <c r="G29" s="119"/>
-      <c r="H29" s="119"/>
-      <c r="I29" s="119"/>
-      <c r="J29" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="K29" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="L29" s="119"/>
-      <c r="M29" s="119"/>
-      <c r="N29" s="119"/>
-      <c r="O29" s="119"/>
-      <c r="P29" s="119"/>
-      <c r="Q29" s="119"/>
-      <c r="S29" s="127"/>
-      <c r="T29" s="127"/>
-      <c r="U29" s="127"/>
-      <c r="V29" s="127"/>
-      <c r="W29" s="127"/>
-      <c r="X29" s="127"/>
-      <c r="Y29" s="127"/>
-      <c r="Z29" s="127"/>
-    </row>
-    <row r="30" s="104" customFormat="1" ht="15" customHeight="1" spans="1:26">
-      <c r="A30" s="115"/>
-      <c r="B30" s="117">
+      <c r="C29" s="111"/>
+      <c r="D29" s="111"/>
+      <c r="E29" s="113"/>
+      <c r="F29" s="113"/>
+      <c r="G29" s="113"/>
+      <c r="H29" s="113"/>
+      <c r="I29" s="113"/>
+      <c r="J29" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="K29" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="L29" s="113"/>
+      <c r="M29" s="113"/>
+      <c r="N29" s="113"/>
+      <c r="O29" s="113"/>
+      <c r="P29" s="113"/>
+      <c r="Q29" s="113"/>
+      <c r="S29" s="121"/>
+      <c r="T29" s="121"/>
+      <c r="U29" s="121"/>
+      <c r="V29" s="121"/>
+      <c r="W29" s="121"/>
+      <c r="X29" s="121"/>
+      <c r="Y29" s="121"/>
+      <c r="Z29" s="121"/>
+    </row>
+    <row r="30" s="98" customFormat="1" ht="15" customHeight="1" spans="1:26">
+      <c r="A30" s="109"/>
+      <c r="B30" s="111">
         <v>5</v>
       </c>
-      <c r="C30" s="117"/>
-      <c r="D30" s="117"/>
-      <c r="E30" s="119"/>
-      <c r="F30" s="119"/>
-      <c r="G30" s="119"/>
-      <c r="H30" s="119"/>
-      <c r="I30" s="119"/>
-      <c r="J30" s="119"/>
-      <c r="K30" s="119"/>
-      <c r="L30" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="M30" s="119"/>
-      <c r="N30" s="119"/>
-      <c r="O30" s="119"/>
-      <c r="P30" s="119"/>
-      <c r="Q30" s="119"/>
-      <c r="S30" s="127"/>
-      <c r="T30" s="127"/>
-      <c r="U30" s="127"/>
-      <c r="V30" s="127"/>
-      <c r="W30" s="127"/>
-      <c r="X30" s="127"/>
-      <c r="Y30" s="127"/>
-      <c r="Z30" s="127"/>
-    </row>
-    <row r="31" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A31" s="115"/>
-      <c r="B31" s="123">
+      <c r="C30" s="111"/>
+      <c r="D30" s="111"/>
+      <c r="E30" s="113"/>
+      <c r="F30" s="113"/>
+      <c r="G30" s="113"/>
+      <c r="H30" s="113"/>
+      <c r="I30" s="113"/>
+      <c r="J30" s="113"/>
+      <c r="K30" s="113"/>
+      <c r="L30" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="M30" s="113"/>
+      <c r="N30" s="113"/>
+      <c r="O30" s="113"/>
+      <c r="P30" s="113"/>
+      <c r="Q30" s="113"/>
+      <c r="S30" s="121"/>
+      <c r="T30" s="121"/>
+      <c r="U30" s="121"/>
+      <c r="V30" s="121"/>
+      <c r="W30" s="121"/>
+      <c r="X30" s="121"/>
+      <c r="Y30" s="121"/>
+      <c r="Z30" s="121"/>
+    </row>
+    <row r="31" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A31" s="109"/>
+      <c r="B31" s="117">
         <v>-1</v>
       </c>
-      <c r="C31" s="124"/>
-      <c r="D31" s="125"/>
-      <c r="E31" s="119"/>
-      <c r="F31" s="119"/>
-      <c r="G31" s="119"/>
-      <c r="H31" s="119"/>
-      <c r="I31" s="119"/>
-      <c r="J31" s="119"/>
-      <c r="K31" s="119"/>
-      <c r="L31" s="119"/>
-      <c r="M31" s="119"/>
-      <c r="N31" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="O31" s="119"/>
-      <c r="P31" s="119"/>
-      <c r="Q31" s="119"/>
-      <c r="S31" s="127"/>
-      <c r="T31" s="127"/>
-      <c r="U31" s="127"/>
-      <c r="V31" s="127"/>
-      <c r="W31" s="127"/>
-      <c r="X31" s="127"/>
-      <c r="Y31" s="127"/>
-      <c r="Z31" s="127"/>
-    </row>
-    <row r="32" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A32" s="115"/>
-      <c r="B32" s="117">
+      <c r="C31" s="118"/>
+      <c r="D31" s="119"/>
+      <c r="E31" s="113"/>
+      <c r="F31" s="113"/>
+      <c r="G31" s="113"/>
+      <c r="H31" s="113"/>
+      <c r="I31" s="113"/>
+      <c r="J31" s="113"/>
+      <c r="K31" s="113"/>
+      <c r="L31" s="113"/>
+      <c r="M31" s="113"/>
+      <c r="N31" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="O31" s="113"/>
+      <c r="P31" s="113"/>
+      <c r="Q31" s="113"/>
+      <c r="S31" s="121"/>
+      <c r="T31" s="121"/>
+      <c r="U31" s="121"/>
+      <c r="V31" s="121"/>
+      <c r="W31" s="121"/>
+      <c r="X31" s="121"/>
+      <c r="Y31" s="121"/>
+      <c r="Z31" s="121"/>
+    </row>
+    <row r="32" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A32" s="109"/>
+      <c r="B32" s="111">
         <v>6</v>
       </c>
-      <c r="C32" s="117"/>
-      <c r="D32" s="117"/>
-      <c r="E32" s="119"/>
-      <c r="F32" s="119"/>
-      <c r="G32" s="119"/>
-      <c r="H32" s="119"/>
-      <c r="I32" s="119"/>
-      <c r="J32" s="119"/>
-      <c r="K32" s="119"/>
-      <c r="L32" s="119"/>
-      <c r="M32" s="119"/>
-      <c r="N32" s="119"/>
-      <c r="O32" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="P32" s="119"/>
-      <c r="Q32" s="119"/>
-      <c r="S32" s="127"/>
-      <c r="T32" s="127"/>
-      <c r="U32" s="127"/>
-      <c r="V32" s="127"/>
-      <c r="W32" s="127"/>
-      <c r="X32" s="127"/>
-      <c r="Y32" s="127"/>
-      <c r="Z32" s="127"/>
-    </row>
-    <row r="33" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A33" s="115" t="s">
+      <c r="C32" s="111"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="113"/>
+      <c r="F32" s="113"/>
+      <c r="G32" s="113"/>
+      <c r="H32" s="113"/>
+      <c r="I32" s="113"/>
+      <c r="J32" s="113"/>
+      <c r="K32" s="113"/>
+      <c r="L32" s="113"/>
+      <c r="M32" s="113"/>
+      <c r="N32" s="113"/>
+      <c r="O32" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="P32" s="113"/>
+      <c r="Q32" s="113"/>
+      <c r="S32" s="121"/>
+      <c r="T32" s="121"/>
+      <c r="U32" s="121"/>
+      <c r="V32" s="121"/>
+      <c r="W32" s="121"/>
+      <c r="X32" s="121"/>
+      <c r="Y32" s="121"/>
+      <c r="Z32" s="121"/>
+    </row>
+    <row r="33" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A33" s="109" t="s">
         <v>50</v>
       </c>
-      <c r="B33" s="123">
+      <c r="B33" s="117">
         <v>3</v>
       </c>
-      <c r="C33" s="124"/>
-      <c r="D33" s="125"/>
-      <c r="E33" s="119"/>
-      <c r="F33" s="119"/>
-      <c r="G33" s="119"/>
-      <c r="H33" s="119"/>
-      <c r="I33" s="119"/>
-      <c r="J33" s="119"/>
-      <c r="K33" s="119"/>
-      <c r="L33" s="119"/>
-      <c r="M33" s="119"/>
-      <c r="N33" s="119"/>
-      <c r="O33" s="119"/>
-      <c r="P33" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q33" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="S33" s="127"/>
-      <c r="T33" s="127"/>
-      <c r="U33" s="127"/>
-      <c r="V33" s="127"/>
-      <c r="W33" s="127"/>
-      <c r="X33" s="127"/>
-      <c r="Y33" s="127"/>
-      <c r="Z33" s="127"/>
-    </row>
-    <row r="34" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A34" s="115"/>
-      <c r="B34" s="105" t="s">
+      <c r="C33" s="118"/>
+      <c r="D33" s="119"/>
+      <c r="E33" s="113"/>
+      <c r="F33" s="113"/>
+      <c r="G33" s="113"/>
+      <c r="H33" s="113"/>
+      <c r="I33" s="113"/>
+      <c r="J33" s="113"/>
+      <c r="K33" s="113"/>
+      <c r="L33" s="113"/>
+      <c r="M33" s="113"/>
+      <c r="N33" s="113"/>
+      <c r="O33" s="113"/>
+      <c r="P33" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q33" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="S33" s="121"/>
+      <c r="T33" s="121"/>
+      <c r="U33" s="121"/>
+      <c r="V33" s="121"/>
+      <c r="W33" s="121"/>
+      <c r="X33" s="121"/>
+      <c r="Y33" s="121"/>
+      <c r="Z33" s="121"/>
+    </row>
+    <row r="34" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A34" s="109"/>
+      <c r="B34" s="99" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="105"/>
-      <c r="D34" s="105"/>
-      <c r="E34" s="118"/>
-      <c r="F34" s="116"/>
-      <c r="G34" s="116"/>
-      <c r="H34" s="116"/>
-      <c r="I34" s="116"/>
-      <c r="J34" s="116"/>
-      <c r="K34" s="116"/>
-      <c r="L34" s="116"/>
-      <c r="M34" s="116"/>
-      <c r="N34" s="116"/>
-      <c r="O34" s="116"/>
-      <c r="P34" s="116"/>
-      <c r="Q34" s="116"/>
-      <c r="S34" s="127"/>
-      <c r="T34" s="127"/>
-      <c r="U34" s="127"/>
-      <c r="V34" s="127"/>
-      <c r="W34" s="127"/>
-      <c r="X34" s="127"/>
-      <c r="Y34" s="127"/>
-      <c r="Z34" s="127"/>
-    </row>
-    <row r="35" s="104" customFormat="1" ht="15" customHeight="1" spans="1:26">
-      <c r="A35" s="115"/>
-      <c r="B35" s="117" t="s">
+      <c r="C34" s="99"/>
+      <c r="D34" s="99"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="110"/>
+      <c r="G34" s="110"/>
+      <c r="H34" s="110"/>
+      <c r="I34" s="110"/>
+      <c r="J34" s="110"/>
+      <c r="K34" s="110"/>
+      <c r="L34" s="110"/>
+      <c r="M34" s="110"/>
+      <c r="N34" s="110"/>
+      <c r="O34" s="110"/>
+      <c r="P34" s="110"/>
+      <c r="Q34" s="110"/>
+      <c r="S34" s="121"/>
+      <c r="T34" s="121"/>
+      <c r="U34" s="121"/>
+      <c r="V34" s="121"/>
+      <c r="W34" s="121"/>
+      <c r="X34" s="121"/>
+      <c r="Y34" s="121"/>
+      <c r="Z34" s="121"/>
+    </row>
+    <row r="35" s="98" customFormat="1" ht="15" customHeight="1" spans="1:26">
+      <c r="A35" s="109"/>
+      <c r="B35" s="111" t="s">
         <v>52</v>
       </c>
-      <c r="C35" s="117"/>
-      <c r="D35" s="117"/>
-      <c r="E35" s="128" t="s">
-        <v>30</v>
-      </c>
-      <c r="F35" s="146"/>
-      <c r="G35" s="128"/>
-      <c r="H35" s="128"/>
-      <c r="I35" s="128"/>
-      <c r="J35" s="128"/>
-      <c r="K35" s="128"/>
-      <c r="L35" s="128"/>
-      <c r="M35" s="146"/>
-      <c r="N35" s="146"/>
-      <c r="O35" s="128"/>
-      <c r="P35" s="128"/>
-      <c r="Q35" s="128"/>
-      <c r="S35" s="127"/>
-      <c r="T35" s="127"/>
-      <c r="U35" s="127"/>
-      <c r="V35" s="127"/>
-      <c r="W35" s="127"/>
-      <c r="X35" s="127"/>
-      <c r="Y35" s="127"/>
-      <c r="Z35" s="127"/>
-    </row>
-    <row r="36" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A36" s="115"/>
-      <c r="B36" s="117" t="s">
+      <c r="C35" s="111"/>
+      <c r="D35" s="111"/>
+      <c r="E35" s="122" t="s">
+        <v>30</v>
+      </c>
+      <c r="F35" s="140"/>
+      <c r="G35" s="122"/>
+      <c r="H35" s="122"/>
+      <c r="I35" s="122"/>
+      <c r="J35" s="122"/>
+      <c r="K35" s="122"/>
+      <c r="L35" s="122"/>
+      <c r="M35" s="140"/>
+      <c r="N35" s="140"/>
+      <c r="O35" s="122"/>
+      <c r="P35" s="122"/>
+      <c r="Q35" s="122"/>
+      <c r="S35" s="121"/>
+      <c r="T35" s="121"/>
+      <c r="U35" s="121"/>
+      <c r="V35" s="121"/>
+      <c r="W35" s="121"/>
+      <c r="X35" s="121"/>
+      <c r="Y35" s="121"/>
+      <c r="Z35" s="121"/>
+    </row>
+    <row r="36" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A36" s="109"/>
+      <c r="B36" s="111" t="s">
         <v>29</v>
       </c>
-      <c r="C36" s="117"/>
-      <c r="D36" s="117"/>
-      <c r="E36" s="128"/>
-      <c r="F36" s="128" t="s">
-        <v>30</v>
-      </c>
-      <c r="G36" s="146" t="s">
-        <v>30</v>
-      </c>
-      <c r="H36" s="146" t="s">
-        <v>30</v>
-      </c>
-      <c r="I36" s="146" t="s">
-        <v>30</v>
-      </c>
-      <c r="J36" s="128"/>
-      <c r="K36" s="128" t="s">
-        <v>30</v>
-      </c>
-      <c r="L36" s="146"/>
-      <c r="M36" s="128"/>
-      <c r="N36" s="128" t="s">
-        <v>30</v>
-      </c>
-      <c r="O36" s="128" t="s">
-        <v>30</v>
-      </c>
-      <c r="P36" s="128" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q36" s="146" t="s">
-        <v>30</v>
-      </c>
-      <c r="S36" s="127"/>
-      <c r="T36" s="127"/>
-      <c r="U36" s="127"/>
-      <c r="V36" s="127"/>
-      <c r="W36" s="127"/>
-      <c r="X36" s="127"/>
-      <c r="Y36" s="127"/>
-      <c r="Z36" s="127"/>
-    </row>
-    <row r="37" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A37" s="115"/>
-      <c r="B37" s="117" t="s">
+      <c r="C36" s="111"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="122"/>
+      <c r="F36" s="122" t="s">
+        <v>30</v>
+      </c>
+      <c r="G36" s="140" t="s">
+        <v>30</v>
+      </c>
+      <c r="H36" s="140" t="s">
+        <v>30</v>
+      </c>
+      <c r="I36" s="140" t="s">
+        <v>30</v>
+      </c>
+      <c r="J36" s="122"/>
+      <c r="K36" s="122" t="s">
+        <v>30</v>
+      </c>
+      <c r="L36" s="140"/>
+      <c r="M36" s="122"/>
+      <c r="N36" s="122" t="s">
+        <v>30</v>
+      </c>
+      <c r="O36" s="122" t="s">
+        <v>30</v>
+      </c>
+      <c r="P36" s="122" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q36" s="140" t="s">
+        <v>30</v>
+      </c>
+      <c r="S36" s="121"/>
+      <c r="T36" s="121"/>
+      <c r="U36" s="121"/>
+      <c r="V36" s="121"/>
+      <c r="W36" s="121"/>
+      <c r="X36" s="121"/>
+      <c r="Y36" s="121"/>
+      <c r="Z36" s="121"/>
+    </row>
+    <row r="37" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A37" s="109"/>
+      <c r="B37" s="111" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="117"/>
-      <c r="D37" s="117"/>
-      <c r="E37" s="128"/>
-      <c r="F37" s="128"/>
-      <c r="G37" s="128"/>
-      <c r="H37" s="128"/>
-      <c r="I37" s="128"/>
-      <c r="J37" s="146" t="s">
-        <v>30</v>
-      </c>
-      <c r="K37" s="128"/>
-      <c r="L37" s="128"/>
-      <c r="M37" s="128"/>
-      <c r="N37" s="128"/>
-      <c r="O37" s="128"/>
-      <c r="P37" s="128"/>
-      <c r="Q37" s="128"/>
-    </row>
-    <row r="38" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A38" s="115"/>
-      <c r="B38" s="117" t="s">
+      <c r="C37" s="111"/>
+      <c r="D37" s="111"/>
+      <c r="E37" s="122"/>
+      <c r="F37" s="122"/>
+      <c r="G37" s="122"/>
+      <c r="H37" s="122"/>
+      <c r="I37" s="122"/>
+      <c r="J37" s="140" t="s">
+        <v>30</v>
+      </c>
+      <c r="K37" s="122"/>
+      <c r="L37" s="122"/>
+      <c r="M37" s="122"/>
+      <c r="N37" s="122"/>
+      <c r="O37" s="122"/>
+      <c r="P37" s="122"/>
+      <c r="Q37" s="122"/>
+    </row>
+    <row r="38" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A38" s="109"/>
+      <c r="B38" s="111" t="s">
         <v>53</v>
       </c>
-      <c r="C38" s="117"/>
-      <c r="D38" s="117"/>
-      <c r="E38" s="128"/>
-      <c r="F38" s="128"/>
-      <c r="G38" s="128"/>
-      <c r="H38" s="128"/>
-      <c r="I38" s="128"/>
-      <c r="J38" s="128"/>
-      <c r="K38" s="146"/>
-      <c r="L38" s="128" t="s">
-        <v>30</v>
-      </c>
-      <c r="M38" s="128"/>
-      <c r="N38" s="128"/>
-      <c r="O38" s="128"/>
-      <c r="P38" s="128"/>
-      <c r="Q38" s="128"/>
-    </row>
-    <row r="39" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A39" s="115"/>
-      <c r="B39" s="117" t="s">
+      <c r="C38" s="111"/>
+      <c r="D38" s="111"/>
+      <c r="E38" s="122"/>
+      <c r="F38" s="122"/>
+      <c r="G38" s="122"/>
+      <c r="H38" s="122"/>
+      <c r="I38" s="122"/>
+      <c r="J38" s="122"/>
+      <c r="K38" s="140"/>
+      <c r="L38" s="122" t="s">
+        <v>30</v>
+      </c>
+      <c r="M38" s="122"/>
+      <c r="N38" s="122"/>
+      <c r="O38" s="122"/>
+      <c r="P38" s="122"/>
+      <c r="Q38" s="122"/>
+    </row>
+    <row r="39" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A39" s="109"/>
+      <c r="B39" s="111" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="117"/>
-      <c r="D39" s="117"/>
-      <c r="E39" s="128"/>
-      <c r="F39" s="128"/>
-      <c r="G39" s="128"/>
-      <c r="H39" s="128"/>
-      <c r="I39" s="128"/>
-      <c r="J39" s="128"/>
-      <c r="K39" s="128"/>
-      <c r="L39" s="128"/>
-      <c r="M39" s="128" t="s">
-        <v>30</v>
-      </c>
-      <c r="N39" s="128"/>
-      <c r="O39" s="128"/>
-      <c r="P39" s="128"/>
-      <c r="Q39" s="128"/>
-    </row>
-    <row r="40" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A40" s="115"/>
-      <c r="B40" s="105" t="s">
+      <c r="C39" s="111"/>
+      <c r="D39" s="111"/>
+      <c r="E39" s="122"/>
+      <c r="F39" s="122"/>
+      <c r="G39" s="122"/>
+      <c r="H39" s="122"/>
+      <c r="I39" s="122"/>
+      <c r="J39" s="122"/>
+      <c r="K39" s="122"/>
+      <c r="L39" s="122"/>
+      <c r="M39" s="122" t="s">
+        <v>30</v>
+      </c>
+      <c r="N39" s="122"/>
+      <c r="O39" s="122"/>
+      <c r="P39" s="122"/>
+      <c r="Q39" s="122"/>
+    </row>
+    <row r="40" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A40" s="109"/>
+      <c r="B40" s="99" t="s">
         <v>55</v>
       </c>
-      <c r="C40" s="105"/>
-      <c r="D40" s="105"/>
-      <c r="E40" s="147"/>
-      <c r="F40" s="147"/>
-      <c r="G40" s="147"/>
-      <c r="H40" s="147"/>
-      <c r="I40" s="147"/>
-      <c r="J40" s="147"/>
-      <c r="K40" s="147"/>
-      <c r="L40" s="147"/>
-      <c r="M40" s="147"/>
-      <c r="N40" s="147"/>
-      <c r="O40" s="147"/>
-      <c r="P40" s="147"/>
-      <c r="Q40" s="147"/>
-    </row>
-    <row r="41" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A41" s="115"/>
-      <c r="B41" s="130" t="s">
+      <c r="C40" s="99"/>
+      <c r="D40" s="99"/>
+      <c r="E40" s="141"/>
+      <c r="F40" s="141"/>
+      <c r="G40" s="141"/>
+      <c r="H40" s="141"/>
+      <c r="I40" s="141"/>
+      <c r="J40" s="141"/>
+      <c r="K40" s="141"/>
+      <c r="L40" s="141"/>
+      <c r="M40" s="141"/>
+      <c r="N40" s="141"/>
+      <c r="O40" s="141"/>
+      <c r="P40" s="141"/>
+      <c r="Q40" s="141"/>
+    </row>
+    <row r="41" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A41" s="109"/>
+      <c r="B41" s="124" t="s">
         <v>56</v>
       </c>
-      <c r="C41" s="130"/>
-      <c r="D41" s="130"/>
-      <c r="E41" s="116" t="s">
+      <c r="C41" s="124"/>
+      <c r="D41" s="124"/>
+      <c r="E41" s="110" t="s">
         <v>57</v>
       </c>
-      <c r="F41" s="116" t="s">
+      <c r="F41" s="110" t="s">
         <v>57</v>
       </c>
-      <c r="G41" s="116" t="s">
+      <c r="G41" s="110" t="s">
         <v>57</v>
       </c>
-      <c r="H41" s="116" t="s">
+      <c r="H41" s="110" t="s">
         <v>57</v>
       </c>
-      <c r="I41" s="116" t="s">
+      <c r="I41" s="110" t="s">
         <v>57</v>
       </c>
-      <c r="J41" s="116" t="s">
+      <c r="J41" s="110" t="s">
         <v>58</v>
       </c>
-      <c r="K41" s="116" t="s">
+      <c r="K41" s="110" t="s">
         <v>58</v>
       </c>
-      <c r="L41" s="116" t="s">
+      <c r="L41" s="110" t="s">
         <v>58</v>
       </c>
-      <c r="M41" s="116" t="s">
+      <c r="M41" s="110" t="s">
         <v>58</v>
       </c>
-      <c r="N41" s="116" t="s">
+      <c r="N41" s="110" t="s">
         <v>58</v>
       </c>
-      <c r="O41" s="116" t="s">
+      <c r="O41" s="110" t="s">
         <v>58</v>
       </c>
-      <c r="P41" s="116" t="s">
+      <c r="P41" s="110" t="s">
         <v>58</v>
       </c>
-      <c r="Q41" s="116" t="s">
+      <c r="Q41" s="110" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="42" s="104" customFormat="1" spans="1:26">
-      <c r="A42" s="115"/>
-      <c r="B42" s="110" t="s">
+    <row r="42" s="98" customFormat="1" spans="1:26">
+      <c r="A42" s="109"/>
+      <c r="B42" s="104" t="s">
         <v>59</v>
       </c>
-      <c r="C42" s="110"/>
-      <c r="D42" s="110"/>
-      <c r="E42" s="131" t="s">
+      <c r="C42" s="104"/>
+      <c r="D42" s="104"/>
+      <c r="E42" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="F42" s="131" t="s">
+      <c r="F42" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="G42" s="131" t="s">
+      <c r="G42" s="125" t="s">
         <v>61</v>
       </c>
-      <c r="H42" s="131" t="s">
+      <c r="H42" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="I42" s="131" t="s">
+      <c r="I42" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="J42" s="131" t="s">
+      <c r="J42" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="K42" s="131" t="s">
+      <c r="K42" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="L42" s="131" t="s">
+      <c r="L42" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="M42" s="131" t="s">
+      <c r="M42" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="N42" s="131" t="s">
+      <c r="N42" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="O42" s="131" t="s">
+      <c r="O42" s="125" t="s">
         <v>61</v>
       </c>
-      <c r="P42" s="131" t="s">
+      <c r="P42" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="Q42" s="131" t="s">
+      <c r="Q42" s="125" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="43" s="104" customFormat="1" ht="30" customHeight="1" spans="1:26">
-      <c r="A43" s="115"/>
-      <c r="B43" s="110" t="s">
+    <row r="43" s="98" customFormat="1" ht="30" customHeight="1" spans="1:26">
+      <c r="A43" s="109"/>
+      <c r="B43" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="C43" s="110"/>
-      <c r="D43" s="110"/>
-      <c r="E43" s="132" t="s">
+      <c r="C43" s="104"/>
+      <c r="D43" s="104"/>
+      <c r="E43" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="F43" s="132" t="s">
+      <c r="F43" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="G43" s="132" t="s">
+      <c r="G43" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="H43" s="132" t="s">
+      <c r="H43" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="I43" s="132" t="s">
+      <c r="I43" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="J43" s="132" t="s">
+      <c r="J43" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="K43" s="132" t="s">
+      <c r="K43" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="L43" s="132" t="s">
+      <c r="L43" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="M43" s="132" t="s">
+      <c r="M43" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="N43" s="132" t="s">
+      <c r="N43" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="O43" s="132" t="s">
+      <c r="O43" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="P43" s="132" t="s">
+      <c r="P43" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="Q43" s="132" t="s">
+      <c r="Q43" s="126" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="44" ht="22.25" spans="1:26">
-      <c r="A44" s="148"/>
-      <c r="B44" s="110" t="s">
+      <c r="A44" s="142"/>
+      <c r="B44" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="C44" s="110"/>
-      <c r="D44" s="110"/>
-      <c r="E44" s="133" t="s">
+      <c r="C44" s="104"/>
+      <c r="D44" s="104"/>
+      <c r="E44" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="F44" s="133" t="s">
+      <c r="F44" s="127" t="s">
         <v>66</v>
       </c>
-      <c r="G44" s="133"/>
-      <c r="H44" s="134" t="s">
+      <c r="G44" s="127"/>
+      <c r="H44" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="I44" s="133" t="s">
+      <c r="I44" s="127" t="s">
         <v>68</v>
       </c>
-      <c r="J44" s="133" t="s">
+      <c r="J44" s="127" t="s">
         <v>69</v>
       </c>
-      <c r="K44" s="133" t="s">
+      <c r="K44" s="127" t="s">
         <v>70</v>
       </c>
-      <c r="L44" s="133" t="s">
+      <c r="L44" s="127" t="s">
         <v>71</v>
       </c>
-      <c r="M44" s="133" t="s">
+      <c r="M44" s="127" t="s">
         <v>72</v>
       </c>
-      <c r="N44" s="133" t="s">
+      <c r="N44" s="127" t="s">
         <v>73</v>
       </c>
-      <c r="O44" s="133" t="s">
+      <c r="O44" s="127" t="s">
         <v>74</v>
       </c>
-      <c r="P44" s="116"/>
-      <c r="Q44" s="133" t="s">
+      <c r="P44" s="110"/>
+      <c r="Q44" s="127" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="47" s="104" customFormat="1" spans="1:26">
-      <c r="B47" s="135" t="s">
+    <row r="47" s="98" customFormat="1" spans="1:26">
+      <c r="B47" s="129" t="s">
         <v>76</v>
       </c>
-      <c r="C47" s="136"/>
-    </row>
-    <row r="48" s="104" customFormat="1" spans="1:26">
-      <c r="B48" s="135" t="s">
+      <c r="C47" s="130"/>
+    </row>
+    <row r="48" s="98" customFormat="1" spans="1:26">
+      <c r="B48" s="129" t="s">
         <v>63</v>
       </c>
-      <c r="C48" s="137">
+      <c r="C48" s="131">
         <v>46063</v>
       </c>
     </row>
-    <row r="49" s="104" customFormat="1" spans="2:3">
-      <c r="B49" s="104" t="s">
+    <row r="49" s="98" customFormat="1" spans="2:3">
+      <c r="B49" s="98" t="s">
         <v>65</v>
       </c>
-      <c r="C49" s="104" t="s">
+      <c r="C49" s="98" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="50" s="104" customFormat="1" spans="2:3">
-      <c r="B50" s="104" t="s">
+    <row r="50" s="98" customFormat="1" spans="2:3">
+      <c r="B50" s="98" t="s">
         <v>66</v>
       </c>
-      <c r="C50" s="104" t="s">
+      <c r="C50" s="98" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="51" s="104" customFormat="1" spans="2:3">
-      <c r="B51" s="104" t="s">
+    <row r="51" s="98" customFormat="1" spans="2:3">
+      <c r="B51" s="98" t="s">
         <v>67</v>
       </c>
-      <c r="C51" s="104" t="s">
+      <c r="C51" s="98" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="52" s="104" customFormat="1" spans="2:3">
-      <c r="B52" s="104" t="s">
+    <row r="52" s="98" customFormat="1" spans="2:3">
+      <c r="B52" s="98" t="s">
         <v>68</v>
       </c>
-      <c r="C52" s="104" t="s">
+      <c r="C52" s="98" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="53" s="104" customFormat="1" spans="2:3">
-      <c r="B53" s="104" t="s">
+    <row r="53" s="98" customFormat="1" spans="2:3">
+      <c r="B53" s="98" t="s">
         <v>69</v>
       </c>
-      <c r="C53" s="104" t="s">
+      <c r="C53" s="98" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="54" s="104" customFormat="1" spans="2:3">
-      <c r="B54" s="104" t="s">
+    <row r="54" s="98" customFormat="1" spans="2:3">
+      <c r="B54" s="98" t="s">
         <v>70</v>
       </c>
-      <c r="C54" s="104" t="s">
+      <c r="C54" s="98" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="55" s="104" customFormat="1" spans="2:3">
-      <c r="B55" s="104" t="s">
+    <row r="55" s="98" customFormat="1" spans="2:3">
+      <c r="B55" s="98" t="s">
         <v>71</v>
       </c>
-      <c r="C55" s="104" t="s">
+      <c r="C55" s="98" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="56" spans="2:3">
-      <c r="B56" s="104" t="s">
+      <c r="B56" s="98" t="s">
         <v>72</v>
       </c>
-      <c r="C56" s="104" t="s">
+      <c r="C56" s="98" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="57" spans="2:3">
-      <c r="B57" s="104" t="s">
+      <c r="B57" s="98" t="s">
         <v>73</v>
       </c>
-      <c r="C57" s="104" t="s">
+      <c r="C57" s="98" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="58" spans="2:3">
-      <c r="B58" s="104" t="s">
+      <c r="B58" s="98" t="s">
         <v>74</v>
       </c>
-      <c r="C58" s="104" t="s">
+      <c r="C58" s="98" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="59" spans="2:3">
-      <c r="B59" s="104" t="s">
+      <c r="B59" s="98" t="s">
         <v>75</v>
       </c>
-      <c r="C59" s="104" t="s">
+      <c r="C59" s="98" t="s">
         <v>84</v>
       </c>
     </row>
@@ -4616,1605 +4513,1605 @@
   <dimension ref="A2:Z67"/>
   <sheetFormatPr defaultColWidth="7.66666666666667" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="17" style="104" customWidth="1"/>
-    <col min="2" max="2" width="9.66666666666667" style="104" customWidth="1"/>
-    <col min="3" max="3" width="12.6666666666667" style="104" customWidth="1"/>
-    <col min="4" max="4" width="9.66666666666667" style="104" customWidth="1"/>
-    <col min="5" max="11" width="4" style="104" customWidth="1"/>
-    <col min="12" max="12" width="3.33333333333333" style="104" customWidth="1"/>
-    <col min="13" max="17" width="4" style="104" customWidth="1"/>
-    <col min="18" max="18" width="2.66666666666667" style="104" customWidth="1"/>
-    <col min="19" max="19" width="9.88888888888889" style="104" customWidth="1"/>
-    <col min="20" max="20" width="21.6666666666667" style="104" customWidth="1"/>
-    <col min="21" max="21" width="14.8888888888889" style="104" customWidth="1"/>
-    <col min="22" max="22" width="15.7777777777778" style="104" customWidth="1"/>
-    <col min="23" max="23" width="18.1111111111111" style="104" customWidth="1"/>
-    <col min="24" max="24" width="42.8888888888889" style="104" customWidth="1"/>
-    <col min="25" max="25" width="28" style="104" customWidth="1"/>
-    <col min="26" max="26" width="8.77777777777778" style="104" customWidth="1"/>
-    <col min="27" max="16384" width="7.66666666666667" style="104"/>
+    <col min="1" max="1" width="17" style="98" customWidth="1"/>
+    <col min="2" max="2" width="9.66666666666667" style="98" customWidth="1"/>
+    <col min="3" max="3" width="12.6666666666667" style="98" customWidth="1"/>
+    <col min="4" max="4" width="9.66666666666667" style="98" customWidth="1"/>
+    <col min="5" max="11" width="4" style="98" customWidth="1"/>
+    <col min="12" max="12" width="3.33333333333333" style="98" customWidth="1"/>
+    <col min="13" max="17" width="4" style="98" customWidth="1"/>
+    <col min="18" max="18" width="2.66666666666667" style="98" customWidth="1"/>
+    <col min="19" max="19" width="9.88888888888889" style="98" customWidth="1"/>
+    <col min="20" max="20" width="21.6666666666667" style="98" customWidth="1"/>
+    <col min="21" max="21" width="14.8888888888889" style="98" customWidth="1"/>
+    <col min="22" max="22" width="15.7777777777778" style="98" customWidth="1"/>
+    <col min="23" max="23" width="18.1111111111111" style="98" customWidth="1"/>
+    <col min="24" max="24" width="42.8888888888889" style="98" customWidth="1"/>
+    <col min="25" max="25" width="28" style="98" customWidth="1"/>
+    <col min="26" max="26" width="8.77777777777778" style="98" customWidth="1"/>
+    <col min="27" max="16384" width="7.66666666666667" style="98"/>
   </cols>
   <sheetData>
-    <row r="2" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
-      <c r="A2" s="105" t="s">
+    <row r="2" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
+      <c r="A2" s="99" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="106"/>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="105" t="s">
+      <c r="B2" s="100"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="108" t="s">
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="102" t="s">
         <v>85</v>
       </c>
-      <c r="M2" s="109"/>
-      <c r="N2" s="109"/>
-      <c r="O2" s="109"/>
-      <c r="P2" s="109"/>
-      <c r="Q2" s="109"/>
-    </row>
-    <row r="3" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
-      <c r="A3" s="105" t="s">
+      <c r="M2" s="103"/>
+      <c r="N2" s="103"/>
+      <c r="O2" s="103"/>
+      <c r="P2" s="103"/>
+      <c r="Q2" s="103"/>
+    </row>
+    <row r="3" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
+      <c r="A3" s="99" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="109" t="s">
+      <c r="B3" s="103" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="105" t="s">
+      <c r="C3" s="101"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="99" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="105"/>
-      <c r="G3" s="105"/>
-      <c r="H3" s="105"/>
-      <c r="I3" s="105"/>
-      <c r="J3" s="105"/>
-      <c r="K3" s="105"/>
-      <c r="L3" s="110" t="s">
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="99"/>
+      <c r="J3" s="99"/>
+      <c r="K3" s="99"/>
+      <c r="L3" s="104" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="110"/>
-      <c r="N3" s="110"/>
-      <c r="O3" s="110"/>
-      <c r="P3" s="110"/>
-      <c r="Q3" s="110"/>
-    </row>
-    <row r="4" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
-      <c r="A4" s="105" t="s">
+      <c r="M3" s="104"/>
+      <c r="N3" s="104"/>
+      <c r="O3" s="104"/>
+      <c r="P3" s="104"/>
+      <c r="Q3" s="104"/>
+    </row>
+    <row r="4" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
+      <c r="A4" s="99" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="109"/>
-      <c r="C4" s="109"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="105" t="s">
+      <c r="B4" s="103"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="105"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="105"/>
-      <c r="I4" s="105"/>
-      <c r="J4" s="105"/>
-      <c r="K4" s="105"/>
-      <c r="L4" s="109">
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="99"/>
+      <c r="K4" s="99"/>
+      <c r="L4" s="103">
         <v>0</v>
       </c>
-      <c r="M4" s="109"/>
-      <c r="N4" s="109"/>
-      <c r="O4" s="109"/>
-      <c r="P4" s="109"/>
-      <c r="Q4" s="109"/>
-    </row>
-    <row r="5" s="104" customFormat="1" ht="71" customHeight="1" spans="1:17">
-      <c r="A5" s="105" t="s">
+      <c r="M4" s="103"/>
+      <c r="N4" s="103"/>
+      <c r="O4" s="103"/>
+      <c r="P4" s="103"/>
+      <c r="Q4" s="103"/>
+    </row>
+    <row r="5" s="98" customFormat="1" ht="71" customHeight="1" spans="1:17">
+      <c r="A5" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="111" t="s">
+      <c r="B5" s="105" t="s">
         <v>86</v>
       </c>
-      <c r="C5" s="111"/>
-      <c r="D5" s="111"/>
-      <c r="E5" s="111"/>
-      <c r="F5" s="111"/>
-      <c r="G5" s="111"/>
-      <c r="H5" s="111"/>
-      <c r="I5" s="111"/>
-      <c r="J5" s="111"/>
-      <c r="K5" s="111"/>
-      <c r="L5" s="111"/>
-      <c r="M5" s="111"/>
-      <c r="N5" s="111"/>
-      <c r="O5" s="111"/>
-      <c r="P5" s="111"/>
-      <c r="Q5" s="111"/>
-    </row>
-    <row r="6" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
-      <c r="A6" s="112" t="s">
+      <c r="C5" s="105"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="105"/>
+      <c r="J5" s="105"/>
+      <c r="K5" s="105"/>
+      <c r="L5" s="105"/>
+      <c r="M5" s="105"/>
+      <c r="N5" s="105"/>
+      <c r="O5" s="105"/>
+      <c r="P5" s="105"/>
+      <c r="Q5" s="105"/>
+    </row>
+    <row r="6" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
+      <c r="A6" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="112" t="s">
+      <c r="B6" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="112"/>
-      <c r="D6" s="112"/>
-      <c r="E6" s="112" t="s">
+      <c r="C6" s="106"/>
+      <c r="D6" s="106"/>
+      <c r="E6" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="112"/>
-      <c r="G6" s="112"/>
-      <c r="H6" s="112"/>
-      <c r="I6" s="112" t="s">
+      <c r="F6" s="106"/>
+      <c r="G6" s="106"/>
+      <c r="H6" s="106"/>
+      <c r="I6" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="112"/>
-      <c r="K6" s="112"/>
-      <c r="L6" s="112" t="s">
+      <c r="J6" s="106"/>
+      <c r="K6" s="106"/>
+      <c r="L6" s="106" t="s">
         <v>13</v>
       </c>
-      <c r="M6" s="112"/>
-      <c r="N6" s="112"/>
-      <c r="O6" s="112"/>
-      <c r="P6" s="112"/>
-      <c r="Q6" s="112"/>
-    </row>
-    <row r="7" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
-      <c r="A7" s="109">
+      <c r="M6" s="106"/>
+      <c r="N6" s="106"/>
+      <c r="O6" s="106"/>
+      <c r="P6" s="106"/>
+      <c r="Q6" s="106"/>
+    </row>
+    <row r="7" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
+      <c r="A7" s="103">
         <f>COUNTIF(E52:Q52,"P")</f>
         <v>4</v>
       </c>
-      <c r="B7" s="109">
+      <c r="B7" s="103">
         <f>COUNTIF(E52:Q52,"F")</f>
         <v>9</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="109">
+      <c r="C7" s="103"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="103">
         <f>L7-A7-B7</f>
         <v>0</v>
       </c>
-      <c r="F7" s="109"/>
-      <c r="G7" s="109"/>
-      <c r="H7" s="109"/>
-      <c r="I7" s="109">
+      <c r="F7" s="103"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="103">
         <f>COUNTIF(E51:Q51,"N")</f>
         <v>4</v>
       </c>
-      <c r="J7" s="109">
+      <c r="J7" s="103">
         <f>COUNTIF(E51:Q51,"A")</f>
         <v>3</v>
       </c>
-      <c r="K7" s="109">
+      <c r="K7" s="103">
         <f>COUNTIF(E51:Q51,"B")</f>
         <v>6</v>
       </c>
-      <c r="L7" s="109">
+      <c r="L7" s="103">
         <f>COUNTA(E51:Q51)</f>
         <v>13</v>
       </c>
-      <c r="M7" s="109"/>
-      <c r="N7" s="109"/>
-      <c r="O7" s="109"/>
-      <c r="P7" s="109"/>
-      <c r="Q7" s="109"/>
-    </row>
-    <row r="9" s="104" customFormat="1" ht="67.5" customHeight="1" spans="1:17">
-      <c r="A9" s="113"/>
-      <c r="B9" s="113"/>
-      <c r="C9" s="113"/>
-      <c r="D9" s="113"/>
-      <c r="E9" s="114" t="s">
+      <c r="M7" s="103"/>
+      <c r="N7" s="103"/>
+      <c r="O7" s="103"/>
+      <c r="P7" s="103"/>
+      <c r="Q7" s="103"/>
+    </row>
+    <row r="9" s="98" customFormat="1" ht="67.5" customHeight="1" spans="1:17">
+      <c r="A9" s="107"/>
+      <c r="B9" s="107"/>
+      <c r="C9" s="107"/>
+      <c r="D9" s="107"/>
+      <c r="E9" s="108" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="114" t="s">
+      <c r="F9" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="114" t="s">
+      <c r="G9" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="114" t="s">
+      <c r="H9" s="108" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="114" t="s">
+      <c r="I9" s="108" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="114" t="s">
+      <c r="J9" s="108" t="s">
         <v>19</v>
       </c>
-      <c r="K9" s="114" t="s">
+      <c r="K9" s="108" t="s">
         <v>20</v>
       </c>
-      <c r="L9" s="114" t="s">
+      <c r="L9" s="108" t="s">
         <v>21</v>
       </c>
-      <c r="M9" s="114" t="s">
+      <c r="M9" s="108" t="s">
         <v>22</v>
       </c>
-      <c r="N9" s="114" t="s">
+      <c r="N9" s="108" t="s">
         <v>23</v>
       </c>
-      <c r="O9" s="114" t="s">
+      <c r="O9" s="108" t="s">
         <v>24</v>
       </c>
-      <c r="P9" s="114" t="s">
+      <c r="P9" s="108" t="s">
         <v>25</v>
       </c>
-      <c r="Q9" s="114" t="s">
+      <c r="Q9" s="108" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
-      <c r="A10" s="115" t="s">
+    <row r="10" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
+      <c r="A10" s="109" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="105" t="s">
+      <c r="B10" s="99" t="s">
         <v>87</v>
       </c>
-      <c r="C10" s="105"/>
-      <c r="D10" s="105"/>
-      <c r="E10" s="116"/>
-      <c r="F10" s="116"/>
-      <c r="G10" s="116"/>
-      <c r="H10" s="116"/>
-      <c r="I10" s="116"/>
-      <c r="J10" s="116"/>
-      <c r="K10" s="116"/>
-      <c r="L10" s="116"/>
-      <c r="M10" s="116"/>
-      <c r="N10" s="116"/>
-      <c r="O10" s="116"/>
-      <c r="P10" s="116"/>
-      <c r="Q10" s="116"/>
-    </row>
-    <row r="11" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
-      <c r="A11" s="115"/>
-      <c r="B11" s="117" t="s">
+      <c r="C10" s="99"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="110"/>
+      <c r="F10" s="110"/>
+      <c r="G10" s="110"/>
+      <c r="H10" s="110"/>
+      <c r="I10" s="110"/>
+      <c r="J10" s="110"/>
+      <c r="K10" s="110"/>
+      <c r="L10" s="110"/>
+      <c r="M10" s="110"/>
+      <c r="N10" s="110"/>
+      <c r="O10" s="110"/>
+      <c r="P10" s="110"/>
+      <c r="Q10" s="110"/>
+    </row>
+    <row r="11" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
+      <c r="A11" s="109"/>
+      <c r="B11" s="111" t="s">
         <v>88</v>
       </c>
-      <c r="C11" s="117"/>
-      <c r="D11" s="117"/>
-      <c r="E11" s="118" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" s="116"/>
-      <c r="G11" s="118"/>
-      <c r="H11" s="118"/>
-      <c r="I11" s="116"/>
-      <c r="J11" s="118"/>
-      <c r="K11" s="116"/>
-      <c r="L11" s="118"/>
-      <c r="M11" s="118"/>
-      <c r="N11" s="118"/>
-      <c r="O11" s="118"/>
-      <c r="P11" s="118"/>
-      <c r="Q11" s="118"/>
-    </row>
-    <row r="12" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
-      <c r="A12" s="115"/>
-      <c r="B12" s="117" t="s">
+      <c r="C11" s="111"/>
+      <c r="D11" s="111"/>
+      <c r="E11" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="110"/>
+      <c r="G11" s="112"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="110"/>
+      <c r="J11" s="112"/>
+      <c r="K11" s="110"/>
+      <c r="L11" s="112"/>
+      <c r="M11" s="112"/>
+      <c r="N11" s="112"/>
+      <c r="O11" s="112"/>
+      <c r="P11" s="112"/>
+      <c r="Q11" s="112"/>
+    </row>
+    <row r="12" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
+      <c r="A12" s="109"/>
+      <c r="B12" s="111" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="117"/>
-      <c r="D12" s="117"/>
-      <c r="E12" s="116"/>
-      <c r="F12" s="118" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="116"/>
-      <c r="H12" s="116"/>
-      <c r="I12" s="116"/>
-      <c r="J12" s="116"/>
-      <c r="K12" s="116"/>
-      <c r="L12" s="116"/>
-      <c r="M12" s="116"/>
-      <c r="N12" s="116"/>
-      <c r="O12" s="116"/>
-      <c r="P12" s="116"/>
-      <c r="Q12" s="116"/>
-    </row>
-    <row r="13" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
-      <c r="A13" s="115"/>
-      <c r="B13" s="117" t="s">
+      <c r="C12" s="111"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="110"/>
+      <c r="F12" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="110"/>
+      <c r="H12" s="110"/>
+      <c r="I12" s="110"/>
+      <c r="J12" s="110"/>
+      <c r="K12" s="110"/>
+      <c r="L12" s="110"/>
+      <c r="M12" s="110"/>
+      <c r="N12" s="110"/>
+      <c r="O12" s="110"/>
+      <c r="P12" s="110"/>
+      <c r="Q12" s="110"/>
+    </row>
+    <row r="13" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
+      <c r="A13" s="109"/>
+      <c r="B13" s="111" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="117"/>
-      <c r="D13" s="117"/>
-      <c r="E13" s="116"/>
-      <c r="F13" s="119"/>
-      <c r="G13" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" s="119"/>
-      <c r="I13" s="118"/>
-      <c r="J13" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="K13" s="118" t="s">
-        <v>30</v>
-      </c>
-      <c r="L13" s="119"/>
-      <c r="M13" s="119"/>
-      <c r="N13" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="O13" s="119"/>
-      <c r="P13" s="119"/>
-      <c r="Q13" s="119"/>
-    </row>
-    <row r="14" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
-      <c r="A14" s="115"/>
-      <c r="B14" s="120" t="s">
+      <c r="C13" s="111"/>
+      <c r="D13" s="111"/>
+      <c r="E13" s="110"/>
+      <c r="F13" s="113"/>
+      <c r="G13" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="113"/>
+      <c r="I13" s="112"/>
+      <c r="J13" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="K13" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="L13" s="113"/>
+      <c r="M13" s="113"/>
+      <c r="N13" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="O13" s="113"/>
+      <c r="P13" s="113"/>
+      <c r="Q13" s="113"/>
+    </row>
+    <row r="14" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
+      <c r="A14" s="109"/>
+      <c r="B14" s="114" t="s">
         <v>90</v>
       </c>
-      <c r="C14" s="121"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="116"/>
-      <c r="F14" s="119"/>
-      <c r="G14" s="119"/>
-      <c r="H14" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="119"/>
-      <c r="J14" s="119"/>
-      <c r="K14" s="119"/>
-      <c r="L14" s="119"/>
-      <c r="M14" s="119"/>
-      <c r="N14" s="119"/>
-      <c r="O14" s="119"/>
-      <c r="P14" s="119"/>
-      <c r="Q14" s="119"/>
-    </row>
-    <row r="15" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
-      <c r="A15" s="115"/>
-      <c r="B15" s="123" t="s">
+      <c r="C14" s="115"/>
+      <c r="D14" s="116"/>
+      <c r="E14" s="110"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="113"/>
+      <c r="H14" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="113"/>
+      <c r="J14" s="113"/>
+      <c r="K14" s="113"/>
+      <c r="L14" s="113"/>
+      <c r="M14" s="113"/>
+      <c r="N14" s="113"/>
+      <c r="O14" s="113"/>
+      <c r="P14" s="113"/>
+      <c r="Q14" s="113"/>
+    </row>
+    <row r="15" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
+      <c r="A15" s="109"/>
+      <c r="B15" s="117" t="s">
         <v>91</v>
       </c>
-      <c r="C15" s="124"/>
-      <c r="D15" s="125"/>
-      <c r="E15" s="116"/>
-      <c r="F15" s="119"/>
-      <c r="G15" s="119"/>
-      <c r="H15" s="119"/>
-      <c r="I15" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="J15" s="119"/>
-      <c r="K15" s="119"/>
-      <c r="L15" s="119"/>
-      <c r="M15" s="119"/>
-      <c r="N15" s="119"/>
-      <c r="O15" s="119"/>
-      <c r="P15" s="119"/>
-      <c r="Q15" s="119"/>
-    </row>
-    <row r="16" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
-      <c r="A16" s="115"/>
-      <c r="B16" s="123" t="s">
+      <c r="C15" s="118"/>
+      <c r="D15" s="119"/>
+      <c r="E15" s="110"/>
+      <c r="F15" s="113"/>
+      <c r="G15" s="113"/>
+      <c r="H15" s="113"/>
+      <c r="I15" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="J15" s="113"/>
+      <c r="K15" s="113"/>
+      <c r="L15" s="113"/>
+      <c r="M15" s="113"/>
+      <c r="N15" s="113"/>
+      <c r="O15" s="113"/>
+      <c r="P15" s="113"/>
+      <c r="Q15" s="113"/>
+    </row>
+    <row r="16" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
+      <c r="A16" s="109"/>
+      <c r="B16" s="117" t="s">
         <v>92</v>
       </c>
-      <c r="C16" s="124"/>
-      <c r="D16" s="125"/>
-      <c r="E16" s="116"/>
-      <c r="F16" s="119"/>
-      <c r="G16" s="119"/>
-      <c r="H16" s="119"/>
-      <c r="I16" s="119"/>
-      <c r="J16" s="119"/>
-      <c r="K16" s="119"/>
-      <c r="L16" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="M16" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="N16" s="119"/>
-      <c r="O16" s="119"/>
-      <c r="P16" s="119"/>
-      <c r="Q16" s="119"/>
-    </row>
-    <row r="17" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A17" s="115"/>
-      <c r="B17" s="123" t="s">
+      <c r="C16" s="118"/>
+      <c r="D16" s="119"/>
+      <c r="E16" s="110"/>
+      <c r="F16" s="113"/>
+      <c r="G16" s="113"/>
+      <c r="H16" s="113"/>
+      <c r="I16" s="113"/>
+      <c r="J16" s="113"/>
+      <c r="K16" s="113"/>
+      <c r="L16" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="M16" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="N16" s="113"/>
+      <c r="O16" s="113"/>
+      <c r="P16" s="113"/>
+      <c r="Q16" s="113"/>
+    </row>
+    <row r="17" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A17" s="109"/>
+      <c r="B17" s="117" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="124"/>
-      <c r="D17" s="125"/>
-      <c r="E17" s="116"/>
-      <c r="F17" s="119"/>
-      <c r="G17" s="119"/>
-      <c r="H17" s="119"/>
-      <c r="I17" s="119"/>
-      <c r="J17" s="119"/>
-      <c r="K17" s="119"/>
-      <c r="L17" s="119"/>
-      <c r="M17" s="119"/>
-      <c r="N17" s="119"/>
-      <c r="O17" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="P17" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q17" s="119" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A18" s="115"/>
-      <c r="B18" s="105" t="s">
+      <c r="C17" s="118"/>
+      <c r="D17" s="119"/>
+      <c r="E17" s="110"/>
+      <c r="F17" s="113"/>
+      <c r="G17" s="113"/>
+      <c r="H17" s="113"/>
+      <c r="I17" s="113"/>
+      <c r="J17" s="113"/>
+      <c r="K17" s="113"/>
+      <c r="L17" s="113"/>
+      <c r="M17" s="113"/>
+      <c r="N17" s="113"/>
+      <c r="O17" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="P17" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q17" s="113" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A18" s="109"/>
+      <c r="B18" s="99" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="105"/>
-      <c r="D18" s="105"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="119"/>
-      <c r="G18" s="119"/>
-      <c r="H18" s="119"/>
-      <c r="I18" s="119"/>
-      <c r="J18" s="119"/>
-      <c r="K18" s="119"/>
-      <c r="L18" s="119"/>
-      <c r="M18" s="119"/>
-      <c r="N18" s="119"/>
-      <c r="O18" s="119"/>
-      <c r="P18" s="119"/>
-      <c r="Q18" s="119"/>
-    </row>
-    <row r="19" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A19" s="115"/>
-      <c r="B19" s="117" t="s">
+      <c r="C18" s="99"/>
+      <c r="D18" s="99"/>
+      <c r="E18" s="110"/>
+      <c r="F18" s="113"/>
+      <c r="G18" s="113"/>
+      <c r="H18" s="113"/>
+      <c r="I18" s="113"/>
+      <c r="J18" s="113"/>
+      <c r="K18" s="113"/>
+      <c r="L18" s="113"/>
+      <c r="M18" s="113"/>
+      <c r="N18" s="113"/>
+      <c r="O18" s="113"/>
+      <c r="P18" s="113"/>
+      <c r="Q18" s="113"/>
+    </row>
+    <row r="19" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A19" s="109"/>
+      <c r="B19" s="111" t="s">
         <v>94</v>
       </c>
-      <c r="C19" s="117"/>
-      <c r="D19" s="117"/>
-      <c r="E19" s="118" t="s">
-        <v>30</v>
-      </c>
-      <c r="F19" s="118"/>
-      <c r="G19" s="119"/>
-      <c r="H19" s="118"/>
-      <c r="I19" s="119"/>
-      <c r="J19" s="119"/>
-      <c r="K19" s="118"/>
-      <c r="L19" s="119"/>
-      <c r="M19" s="119"/>
-      <c r="N19" s="119"/>
-      <c r="O19" s="119"/>
-      <c r="P19" s="119"/>
-      <c r="Q19" s="119"/>
-    </row>
-    <row r="20" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A20" s="115"/>
-      <c r="B20" s="117" t="s">
+      <c r="C19" s="111"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="112"/>
+      <c r="G19" s="113"/>
+      <c r="H19" s="112"/>
+      <c r="I19" s="113"/>
+      <c r="J19" s="113"/>
+      <c r="K19" s="112"/>
+      <c r="L19" s="113"/>
+      <c r="M19" s="113"/>
+      <c r="N19" s="113"/>
+      <c r="O19" s="113"/>
+      <c r="P19" s="113"/>
+      <c r="Q19" s="113"/>
+    </row>
+    <row r="20" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A20" s="109"/>
+      <c r="B20" s="111" t="s">
         <v>95</v>
       </c>
-      <c r="C20" s="117"/>
-      <c r="D20" s="117"/>
-      <c r="E20" s="116"/>
-      <c r="F20" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="G20" s="118"/>
-      <c r="H20" s="119"/>
-      <c r="I20" s="118"/>
-      <c r="J20" s="119"/>
-      <c r="K20" s="119"/>
-      <c r="L20" s="119"/>
-      <c r="M20" s="119"/>
-      <c r="N20" s="119"/>
-      <c r="O20" s="119"/>
-      <c r="P20" s="119"/>
-      <c r="Q20" s="119"/>
-    </row>
-    <row r="21" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A21" s="115"/>
-      <c r="B21" s="117" t="s">
+      <c r="C20" s="111"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="110"/>
+      <c r="F20" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" s="112"/>
+      <c r="H20" s="113"/>
+      <c r="I20" s="112"/>
+      <c r="J20" s="113"/>
+      <c r="K20" s="113"/>
+      <c r="L20" s="113"/>
+      <c r="M20" s="113"/>
+      <c r="N20" s="113"/>
+      <c r="O20" s="113"/>
+      <c r="P20" s="113"/>
+      <c r="Q20" s="113"/>
+    </row>
+    <row r="21" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A21" s="109"/>
+      <c r="B21" s="111" t="s">
         <v>90</v>
       </c>
-      <c r="C21" s="117"/>
-      <c r="D21" s="117"/>
-      <c r="E21" s="116"/>
-      <c r="F21" s="119"/>
-      <c r="G21" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="H21" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" s="119"/>
-      <c r="J21" s="119"/>
-      <c r="K21" s="119"/>
-      <c r="L21" s="119"/>
-      <c r="M21" s="119"/>
-      <c r="N21" s="119"/>
-      <c r="O21" s="119"/>
-      <c r="P21" s="119"/>
-      <c r="Q21" s="119"/>
-      <c r="S21" s="126"/>
-      <c r="T21" s="126"/>
-      <c r="U21" s="126"/>
-      <c r="V21" s="126"/>
-      <c r="W21" s="126"/>
-      <c r="X21" s="126"/>
-      <c r="Y21" s="126"/>
-      <c r="Z21" s="126"/>
-    </row>
-    <row r="22" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A22" s="115"/>
-      <c r="B22" s="117" t="s">
+      <c r="C21" s="111"/>
+      <c r="D21" s="111"/>
+      <c r="E21" s="110"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="113"/>
+      <c r="J21" s="113"/>
+      <c r="K21" s="113"/>
+      <c r="L21" s="113"/>
+      <c r="M21" s="113"/>
+      <c r="N21" s="113"/>
+      <c r="O21" s="113"/>
+      <c r="P21" s="113"/>
+      <c r="Q21" s="113"/>
+      <c r="S21" s="120"/>
+      <c r="T21" s="120"/>
+      <c r="U21" s="120"/>
+      <c r="V21" s="120"/>
+      <c r="W21" s="120"/>
+      <c r="X21" s="120"/>
+      <c r="Y21" s="120"/>
+      <c r="Z21" s="120"/>
+    </row>
+    <row r="22" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A22" s="109"/>
+      <c r="B22" s="111" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="117"/>
-      <c r="D22" s="117"/>
-      <c r="E22" s="116"/>
-      <c r="F22" s="119"/>
-      <c r="G22" s="119"/>
-      <c r="H22" s="119"/>
-      <c r="I22" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="J22" s="118"/>
-      <c r="K22" s="119"/>
-      <c r="L22" s="119"/>
-      <c r="M22" s="119"/>
-      <c r="N22" s="119"/>
-      <c r="O22" s="119"/>
-      <c r="P22" s="119"/>
-      <c r="Q22" s="119"/>
-    </row>
-    <row r="23" s="104" customFormat="1" ht="15" customHeight="1" spans="1:26">
-      <c r="A23" s="115"/>
-      <c r="B23" s="117" t="s">
+      <c r="C22" s="111"/>
+      <c r="D22" s="111"/>
+      <c r="E22" s="110"/>
+      <c r="F22" s="113"/>
+      <c r="G22" s="113"/>
+      <c r="H22" s="113"/>
+      <c r="I22" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="J22" s="112"/>
+      <c r="K22" s="113"/>
+      <c r="L22" s="113"/>
+      <c r="M22" s="113"/>
+      <c r="N22" s="113"/>
+      <c r="O22" s="113"/>
+      <c r="P22" s="113"/>
+      <c r="Q22" s="113"/>
+    </row>
+    <row r="23" s="98" customFormat="1" ht="15" customHeight="1" spans="1:26">
+      <c r="A23" s="109"/>
+      <c r="B23" s="111" t="s">
         <v>91</v>
       </c>
-      <c r="C23" s="117"/>
-      <c r="D23" s="117"/>
-      <c r="E23" s="116"/>
-      <c r="F23" s="119"/>
-      <c r="G23" s="119"/>
-      <c r="H23" s="119"/>
-      <c r="I23" s="119"/>
-      <c r="J23" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="K23" s="119"/>
-      <c r="L23" s="118"/>
-      <c r="M23" s="119"/>
-      <c r="N23" s="119"/>
-      <c r="O23" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="P23" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q23" s="119"/>
-    </row>
-    <row r="24" s="104" customFormat="1" ht="15" customHeight="1" spans="1:26">
-      <c r="A24" s="115"/>
-      <c r="B24" s="117" t="s">
+      <c r="C23" s="111"/>
+      <c r="D23" s="111"/>
+      <c r="E23" s="110"/>
+      <c r="F23" s="113"/>
+      <c r="G23" s="113"/>
+      <c r="H23" s="113"/>
+      <c r="I23" s="113"/>
+      <c r="J23" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" s="113"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="113"/>
+      <c r="N23" s="113"/>
+      <c r="O23" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="P23" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q23" s="113"/>
+    </row>
+    <row r="24" s="98" customFormat="1" ht="15" customHeight="1" spans="1:26">
+      <c r="A24" s="109"/>
+      <c r="B24" s="111" t="s">
         <v>96</v>
       </c>
-      <c r="C24" s="117"/>
-      <c r="D24" s="117"/>
-      <c r="E24" s="116"/>
-      <c r="F24" s="119"/>
-      <c r="G24" s="119"/>
-      <c r="H24" s="119"/>
-      <c r="I24" s="119"/>
-      <c r="J24" s="119"/>
-      <c r="K24" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="L24" s="119"/>
-      <c r="M24" s="118"/>
-      <c r="N24" s="119"/>
-      <c r="O24" s="119"/>
-      <c r="P24" s="119"/>
-      <c r="Q24" s="119"/>
-      <c r="S24" s="127"/>
-      <c r="T24" s="127"/>
-      <c r="U24" s="127"/>
-      <c r="V24" s="127"/>
-      <c r="W24" s="127"/>
-      <c r="X24" s="127"/>
-      <c r="Y24" s="127"/>
-      <c r="Z24" s="127"/>
-    </row>
-    <row r="25" s="104" customFormat="1" ht="15" customHeight="1" spans="1:26">
-      <c r="A25" s="115"/>
-      <c r="B25" s="117" t="s">
+      <c r="C24" s="111"/>
+      <c r="D24" s="111"/>
+      <c r="E24" s="110"/>
+      <c r="F24" s="113"/>
+      <c r="G24" s="113"/>
+      <c r="H24" s="113"/>
+      <c r="I24" s="113"/>
+      <c r="J24" s="113"/>
+      <c r="K24" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="L24" s="113"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="113"/>
+      <c r="O24" s="113"/>
+      <c r="P24" s="113"/>
+      <c r="Q24" s="113"/>
+      <c r="S24" s="121"/>
+      <c r="T24" s="121"/>
+      <c r="U24" s="121"/>
+      <c r="V24" s="121"/>
+      <c r="W24" s="121"/>
+      <c r="X24" s="121"/>
+      <c r="Y24" s="121"/>
+      <c r="Z24" s="121"/>
+    </row>
+    <row r="25" s="98" customFormat="1" ht="15" customHeight="1" spans="1:26">
+      <c r="A25" s="109"/>
+      <c r="B25" s="111" t="s">
         <v>97</v>
       </c>
-      <c r="C25" s="117"/>
-      <c r="D25" s="117"/>
-      <c r="E25" s="116"/>
-      <c r="F25" s="119"/>
-      <c r="G25" s="119"/>
-      <c r="H25" s="119"/>
-      <c r="I25" s="119"/>
-      <c r="J25" s="119"/>
-      <c r="K25" s="119"/>
-      <c r="L25" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="M25" s="119"/>
-      <c r="N25" s="118"/>
-      <c r="O25" s="119"/>
-      <c r="P25" s="119"/>
-      <c r="Q25" s="119"/>
-      <c r="S25" s="127"/>
-      <c r="T25" s="127"/>
-      <c r="U25" s="127"/>
-      <c r="V25" s="127"/>
-      <c r="W25" s="127"/>
-      <c r="X25" s="127"/>
-      <c r="Y25" s="127"/>
-      <c r="Z25" s="127"/>
-    </row>
-    <row r="26" s="104" customFormat="1" ht="15" customHeight="1" spans="1:26">
-      <c r="A26" s="115"/>
-      <c r="B26" s="117" t="s">
+      <c r="C25" s="111"/>
+      <c r="D25" s="111"/>
+      <c r="E25" s="110"/>
+      <c r="F25" s="113"/>
+      <c r="G25" s="113"/>
+      <c r="H25" s="113"/>
+      <c r="I25" s="113"/>
+      <c r="J25" s="113"/>
+      <c r="K25" s="113"/>
+      <c r="L25" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="M25" s="113"/>
+      <c r="N25" s="112"/>
+      <c r="O25" s="113"/>
+      <c r="P25" s="113"/>
+      <c r="Q25" s="113"/>
+      <c r="S25" s="121"/>
+      <c r="T25" s="121"/>
+      <c r="U25" s="121"/>
+      <c r="V25" s="121"/>
+      <c r="W25" s="121"/>
+      <c r="X25" s="121"/>
+      <c r="Y25" s="121"/>
+      <c r="Z25" s="121"/>
+    </row>
+    <row r="26" s="98" customFormat="1" ht="15" customHeight="1" spans="1:26">
+      <c r="A26" s="109"/>
+      <c r="B26" s="111" t="s">
         <v>98</v>
       </c>
-      <c r="C26" s="117"/>
-      <c r="D26" s="117"/>
-      <c r="E26" s="116"/>
-      <c r="F26" s="119"/>
-      <c r="G26" s="119"/>
-      <c r="H26" s="119"/>
-      <c r="I26" s="119"/>
-      <c r="J26" s="119"/>
-      <c r="K26" s="119"/>
-      <c r="L26" s="119"/>
-      <c r="M26" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="N26" s="119"/>
-      <c r="O26" s="118"/>
-      <c r="P26" s="119"/>
-      <c r="Q26" s="119"/>
-      <c r="S26" s="127"/>
-      <c r="T26" s="127"/>
-      <c r="U26" s="127"/>
-      <c r="V26" s="127"/>
-      <c r="W26" s="127"/>
-      <c r="X26" s="127"/>
-      <c r="Y26" s="127"/>
-      <c r="Z26" s="127"/>
-    </row>
-    <row r="27" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A27" s="115"/>
-      <c r="B27" s="123" t="s">
+      <c r="C26" s="111"/>
+      <c r="D26" s="111"/>
+      <c r="E26" s="110"/>
+      <c r="F26" s="113"/>
+      <c r="G26" s="113"/>
+      <c r="H26" s="113"/>
+      <c r="I26" s="113"/>
+      <c r="J26" s="113"/>
+      <c r="K26" s="113"/>
+      <c r="L26" s="113"/>
+      <c r="M26" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="N26" s="113"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="113"/>
+      <c r="Q26" s="113"/>
+      <c r="S26" s="121"/>
+      <c r="T26" s="121"/>
+      <c r="U26" s="121"/>
+      <c r="V26" s="121"/>
+      <c r="W26" s="121"/>
+      <c r="X26" s="121"/>
+      <c r="Y26" s="121"/>
+      <c r="Z26" s="121"/>
+    </row>
+    <row r="27" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A27" s="109"/>
+      <c r="B27" s="117" t="s">
         <v>89</v>
       </c>
-      <c r="C27" s="124"/>
-      <c r="D27" s="125"/>
-      <c r="E27" s="116"/>
-      <c r="F27" s="119"/>
-      <c r="G27" s="119"/>
-      <c r="H27" s="119"/>
-      <c r="I27" s="119"/>
-      <c r="J27" s="119"/>
-      <c r="K27" s="119"/>
-      <c r="L27" s="119"/>
-      <c r="M27" s="119"/>
-      <c r="N27" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="O27" s="119"/>
-      <c r="P27" s="119"/>
-      <c r="Q27" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="S27" s="127"/>
-      <c r="T27" s="127"/>
-      <c r="U27" s="127"/>
-      <c r="V27" s="127"/>
-      <c r="W27" s="127"/>
-      <c r="X27" s="127"/>
-      <c r="Y27" s="127"/>
-      <c r="Z27" s="127"/>
-    </row>
-    <row r="28" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A28" s="115"/>
-      <c r="B28" s="105" t="s">
+      <c r="C27" s="118"/>
+      <c r="D27" s="119"/>
+      <c r="E27" s="110"/>
+      <c r="F27" s="113"/>
+      <c r="G27" s="113"/>
+      <c r="H27" s="113"/>
+      <c r="I27" s="113"/>
+      <c r="J27" s="113"/>
+      <c r="K27" s="113"/>
+      <c r="L27" s="113"/>
+      <c r="M27" s="113"/>
+      <c r="N27" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="O27" s="113"/>
+      <c r="P27" s="113"/>
+      <c r="Q27" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="S27" s="121"/>
+      <c r="T27" s="121"/>
+      <c r="U27" s="121"/>
+      <c r="V27" s="121"/>
+      <c r="W27" s="121"/>
+      <c r="X27" s="121"/>
+      <c r="Y27" s="121"/>
+      <c r="Z27" s="121"/>
+    </row>
+    <row r="28" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A28" s="109"/>
+      <c r="B28" s="99" t="s">
         <v>99</v>
       </c>
-      <c r="C28" s="105"/>
-      <c r="D28" s="105"/>
-      <c r="E28" s="116"/>
-      <c r="F28" s="119"/>
-      <c r="G28" s="119"/>
-      <c r="H28" s="119"/>
-      <c r="I28" s="119"/>
-      <c r="J28" s="119"/>
-      <c r="K28" s="119"/>
-      <c r="L28" s="119"/>
-      <c r="M28" s="119"/>
-      <c r="N28" s="119"/>
-      <c r="O28" s="119"/>
-      <c r="P28" s="119"/>
-      <c r="Q28" s="119"/>
-      <c r="S28" s="127"/>
-      <c r="T28" s="127"/>
-      <c r="U28" s="127"/>
-      <c r="V28" s="127"/>
-      <c r="W28" s="127"/>
-      <c r="X28" s="127"/>
-      <c r="Y28" s="127"/>
-      <c r="Z28" s="127"/>
-    </row>
-    <row r="29" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A29" s="115"/>
-      <c r="B29" s="117" t="s">
+      <c r="C28" s="99"/>
+      <c r="D28" s="99"/>
+      <c r="E28" s="110"/>
+      <c r="F28" s="113"/>
+      <c r="G28" s="113"/>
+      <c r="H28" s="113"/>
+      <c r="I28" s="113"/>
+      <c r="J28" s="113"/>
+      <c r="K28" s="113"/>
+      <c r="L28" s="113"/>
+      <c r="M28" s="113"/>
+      <c r="N28" s="113"/>
+      <c r="O28" s="113"/>
+      <c r="P28" s="113"/>
+      <c r="Q28" s="113"/>
+      <c r="S28" s="121"/>
+      <c r="T28" s="121"/>
+      <c r="U28" s="121"/>
+      <c r="V28" s="121"/>
+      <c r="W28" s="121"/>
+      <c r="X28" s="121"/>
+      <c r="Y28" s="121"/>
+      <c r="Z28" s="121"/>
+    </row>
+    <row r="29" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A29" s="109"/>
+      <c r="B29" s="111" t="s">
         <v>100</v>
       </c>
-      <c r="C29" s="117"/>
-      <c r="D29" s="117"/>
-      <c r="E29" s="118" t="s">
-        <v>30</v>
-      </c>
-      <c r="F29" s="119"/>
-      <c r="G29" s="118"/>
-      <c r="H29" s="119"/>
-      <c r="I29" s="119"/>
-      <c r="J29" s="119"/>
-      <c r="K29" s="118"/>
-      <c r="L29" s="119"/>
-      <c r="M29" s="119"/>
-      <c r="N29" s="119"/>
-      <c r="O29" s="119"/>
-      <c r="P29" s="119"/>
-      <c r="Q29" s="119"/>
-      <c r="S29" s="127"/>
-      <c r="T29" s="127"/>
-      <c r="U29" s="127"/>
-      <c r="V29" s="127"/>
-      <c r="W29" s="127"/>
-      <c r="X29" s="127"/>
-      <c r="Y29" s="127"/>
-      <c r="Z29" s="127"/>
-    </row>
-    <row r="30" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A30" s="115"/>
-      <c r="B30" s="117" t="s">
+      <c r="C29" s="111"/>
+      <c r="D29" s="111"/>
+      <c r="E29" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="F29" s="113"/>
+      <c r="G29" s="112"/>
+      <c r="H29" s="113"/>
+      <c r="I29" s="113"/>
+      <c r="J29" s="113"/>
+      <c r="K29" s="112"/>
+      <c r="L29" s="113"/>
+      <c r="M29" s="113"/>
+      <c r="N29" s="113"/>
+      <c r="O29" s="113"/>
+      <c r="P29" s="113"/>
+      <c r="Q29" s="113"/>
+      <c r="S29" s="121"/>
+      <c r="T29" s="121"/>
+      <c r="U29" s="121"/>
+      <c r="V29" s="121"/>
+      <c r="W29" s="121"/>
+      <c r="X29" s="121"/>
+      <c r="Y29" s="121"/>
+      <c r="Z29" s="121"/>
+    </row>
+    <row r="30" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A30" s="109"/>
+      <c r="B30" s="111" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="117"/>
-      <c r="D30" s="117"/>
-      <c r="E30" s="116"/>
-      <c r="F30" s="118" t="s">
-        <v>30</v>
-      </c>
-      <c r="G30" s="119"/>
-      <c r="H30" s="119"/>
-      <c r="I30" s="119"/>
-      <c r="J30" s="119"/>
-      <c r="K30" s="119"/>
-      <c r="L30" s="119"/>
-      <c r="M30" s="119"/>
-      <c r="N30" s="119"/>
-      <c r="O30" s="119"/>
-      <c r="P30" s="119"/>
-      <c r="Q30" s="119"/>
-      <c r="S30" s="127"/>
-      <c r="T30" s="127"/>
-      <c r="U30" s="127"/>
-      <c r="V30" s="127"/>
-      <c r="W30" s="127"/>
-      <c r="X30" s="127"/>
-      <c r="Y30" s="127"/>
-      <c r="Z30" s="127"/>
-    </row>
-    <row r="31" s="104" customFormat="1" ht="15" customHeight="1" spans="1:26">
-      <c r="A31" s="115"/>
-      <c r="B31" s="117" t="s">
+      <c r="C30" s="111"/>
+      <c r="D30" s="111"/>
+      <c r="E30" s="110"/>
+      <c r="F30" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="G30" s="113"/>
+      <c r="H30" s="113"/>
+      <c r="I30" s="113"/>
+      <c r="J30" s="113"/>
+      <c r="K30" s="113"/>
+      <c r="L30" s="113"/>
+      <c r="M30" s="113"/>
+      <c r="N30" s="113"/>
+      <c r="O30" s="113"/>
+      <c r="P30" s="113"/>
+      <c r="Q30" s="113"/>
+      <c r="S30" s="121"/>
+      <c r="T30" s="121"/>
+      <c r="U30" s="121"/>
+      <c r="V30" s="121"/>
+      <c r="W30" s="121"/>
+      <c r="X30" s="121"/>
+      <c r="Y30" s="121"/>
+      <c r="Z30" s="121"/>
+    </row>
+    <row r="31" s="98" customFormat="1" ht="15" customHeight="1" spans="1:26">
+      <c r="A31" s="109"/>
+      <c r="B31" s="111" t="s">
         <v>95</v>
       </c>
-      <c r="C31" s="117"/>
-      <c r="D31" s="117"/>
-      <c r="E31" s="116"/>
-      <c r="F31" s="119"/>
-      <c r="G31" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="H31" s="118"/>
-      <c r="I31" s="118"/>
-      <c r="J31" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="K31" s="119"/>
-      <c r="L31" s="119"/>
-      <c r="M31" s="119"/>
-      <c r="N31" s="119"/>
-      <c r="O31" s="119"/>
-      <c r="P31" s="119"/>
-      <c r="Q31" s="119"/>
-      <c r="S31" s="127"/>
-      <c r="T31" s="127"/>
-      <c r="U31" s="127"/>
-      <c r="V31" s="127"/>
-      <c r="W31" s="127"/>
-      <c r="X31" s="127"/>
-      <c r="Y31" s="127"/>
-      <c r="Z31" s="127"/>
-    </row>
-    <row r="32" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A32" s="115"/>
-      <c r="B32" s="117" t="s">
+      <c r="C31" s="111"/>
+      <c r="D31" s="111"/>
+      <c r="E31" s="110"/>
+      <c r="F31" s="113"/>
+      <c r="G31" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="H31" s="112"/>
+      <c r="I31" s="112"/>
+      <c r="J31" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="K31" s="113"/>
+      <c r="L31" s="113"/>
+      <c r="M31" s="113"/>
+      <c r="N31" s="113"/>
+      <c r="O31" s="113"/>
+      <c r="P31" s="113"/>
+      <c r="Q31" s="113"/>
+      <c r="S31" s="121"/>
+      <c r="T31" s="121"/>
+      <c r="U31" s="121"/>
+      <c r="V31" s="121"/>
+      <c r="W31" s="121"/>
+      <c r="X31" s="121"/>
+      <c r="Y31" s="121"/>
+      <c r="Z31" s="121"/>
+    </row>
+    <row r="32" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A32" s="109"/>
+      <c r="B32" s="111" t="s">
         <v>90</v>
       </c>
-      <c r="C32" s="117"/>
-      <c r="D32" s="117"/>
-      <c r="E32" s="116"/>
-      <c r="F32" s="119"/>
-      <c r="G32" s="119"/>
-      <c r="H32" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="I32" s="119"/>
-      <c r="J32" s="118"/>
-      <c r="K32" s="119"/>
-      <c r="L32" s="119"/>
-      <c r="M32" s="119"/>
-      <c r="N32" s="119"/>
-      <c r="O32" s="119"/>
-      <c r="P32" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q32" s="119"/>
-      <c r="S32" s="127"/>
-      <c r="T32" s="127"/>
-      <c r="U32" s="127"/>
-      <c r="V32" s="127"/>
-      <c r="W32" s="127"/>
-      <c r="X32" s="127"/>
-      <c r="Y32" s="127"/>
-      <c r="Z32" s="127"/>
-    </row>
-    <row r="33" s="104" customFormat="1" ht="15" customHeight="1" spans="1:26">
-      <c r="A33" s="115"/>
-      <c r="B33" s="117" t="s">
+      <c r="C32" s="111"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="110"/>
+      <c r="F32" s="113"/>
+      <c r="G32" s="113"/>
+      <c r="H32" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="I32" s="113"/>
+      <c r="J32" s="112"/>
+      <c r="K32" s="113"/>
+      <c r="L32" s="113"/>
+      <c r="M32" s="113"/>
+      <c r="N32" s="113"/>
+      <c r="O32" s="113"/>
+      <c r="P32" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q32" s="113"/>
+      <c r="S32" s="121"/>
+      <c r="T32" s="121"/>
+      <c r="U32" s="121"/>
+      <c r="V32" s="121"/>
+      <c r="W32" s="121"/>
+      <c r="X32" s="121"/>
+      <c r="Y32" s="121"/>
+      <c r="Z32" s="121"/>
+    </row>
+    <row r="33" s="98" customFormat="1" ht="15" customHeight="1" spans="1:26">
+      <c r="A33" s="109"/>
+      <c r="B33" s="111" t="s">
         <v>96</v>
       </c>
-      <c r="C33" s="117"/>
-      <c r="D33" s="117"/>
-      <c r="E33" s="116"/>
-      <c r="F33" s="119"/>
-      <c r="G33" s="119"/>
-      <c r="H33" s="119"/>
-      <c r="I33" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="J33" s="119"/>
-      <c r="K33" s="119"/>
-      <c r="L33" s="118"/>
-      <c r="M33" s="119"/>
-      <c r="N33" s="119"/>
-      <c r="O33" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="P33" s="118"/>
-      <c r="Q33" s="119"/>
-      <c r="S33" s="127"/>
-      <c r="T33" s="127"/>
-      <c r="U33" s="127"/>
-      <c r="V33" s="127"/>
-      <c r="W33" s="127"/>
-      <c r="X33" s="127"/>
-      <c r="Y33" s="127"/>
-      <c r="Z33" s="127"/>
-    </row>
-    <row r="34" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A34" s="115"/>
-      <c r="B34" s="117" t="s">
+      <c r="C33" s="111"/>
+      <c r="D33" s="111"/>
+      <c r="E33" s="110"/>
+      <c r="F33" s="113"/>
+      <c r="G33" s="113"/>
+      <c r="H33" s="113"/>
+      <c r="I33" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="J33" s="113"/>
+      <c r="K33" s="113"/>
+      <c r="L33" s="112"/>
+      <c r="M33" s="113"/>
+      <c r="N33" s="113"/>
+      <c r="O33" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="P33" s="112"/>
+      <c r="Q33" s="113"/>
+      <c r="S33" s="121"/>
+      <c r="T33" s="121"/>
+      <c r="U33" s="121"/>
+      <c r="V33" s="121"/>
+      <c r="W33" s="121"/>
+      <c r="X33" s="121"/>
+      <c r="Y33" s="121"/>
+      <c r="Z33" s="121"/>
+    </row>
+    <row r="34" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A34" s="109"/>
+      <c r="B34" s="111" t="s">
         <v>91</v>
       </c>
-      <c r="C34" s="117"/>
-      <c r="D34" s="117"/>
-      <c r="E34" s="116"/>
-      <c r="F34" s="119"/>
-      <c r="G34" s="119"/>
-      <c r="H34" s="119"/>
-      <c r="I34" s="119"/>
-      <c r="J34" s="119"/>
-      <c r="K34" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="L34" s="119"/>
-      <c r="M34" s="119"/>
-      <c r="N34" s="118"/>
-      <c r="O34" s="119"/>
-      <c r="P34" s="119"/>
-      <c r="Q34" s="119"/>
-      <c r="S34" s="127"/>
-      <c r="T34" s="127"/>
-      <c r="U34" s="127"/>
-      <c r="V34" s="127"/>
-      <c r="W34" s="127"/>
-      <c r="X34" s="127"/>
-      <c r="Y34" s="127"/>
-      <c r="Z34" s="127"/>
-    </row>
-    <row r="35" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A35" s="115"/>
-      <c r="B35" s="117" t="s">
+      <c r="C34" s="111"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="110"/>
+      <c r="F34" s="113"/>
+      <c r="G34" s="113"/>
+      <c r="H34" s="113"/>
+      <c r="I34" s="113"/>
+      <c r="J34" s="113"/>
+      <c r="K34" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="L34" s="113"/>
+      <c r="M34" s="113"/>
+      <c r="N34" s="112"/>
+      <c r="O34" s="113"/>
+      <c r="P34" s="113"/>
+      <c r="Q34" s="113"/>
+      <c r="S34" s="121"/>
+      <c r="T34" s="121"/>
+      <c r="U34" s="121"/>
+      <c r="V34" s="121"/>
+      <c r="W34" s="121"/>
+      <c r="X34" s="121"/>
+      <c r="Y34" s="121"/>
+      <c r="Z34" s="121"/>
+    </row>
+    <row r="35" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A35" s="109"/>
+      <c r="B35" s="111" t="s">
         <v>102</v>
       </c>
-      <c r="C35" s="117"/>
-      <c r="D35" s="117"/>
-      <c r="E35" s="116"/>
-      <c r="F35" s="119"/>
-      <c r="G35" s="119"/>
-      <c r="H35" s="119"/>
-      <c r="I35" s="119"/>
-      <c r="J35" s="119"/>
-      <c r="K35" s="119"/>
-      <c r="L35" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="M35" s="119"/>
-      <c r="N35" s="119"/>
-      <c r="O35" s="118"/>
-      <c r="P35" s="119"/>
-      <c r="Q35" s="119"/>
-      <c r="S35" s="127"/>
-      <c r="T35" s="127"/>
-      <c r="U35" s="127"/>
-      <c r="V35" s="127"/>
-      <c r="W35" s="127"/>
-      <c r="X35" s="127"/>
-      <c r="Y35" s="127"/>
-      <c r="Z35" s="127"/>
-    </row>
-    <row r="36" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A36" s="115"/>
-      <c r="B36" s="117" t="s">
+      <c r="C35" s="111"/>
+      <c r="D35" s="111"/>
+      <c r="E35" s="110"/>
+      <c r="F35" s="113"/>
+      <c r="G35" s="113"/>
+      <c r="H35" s="113"/>
+      <c r="I35" s="113"/>
+      <c r="J35" s="113"/>
+      <c r="K35" s="113"/>
+      <c r="L35" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="M35" s="113"/>
+      <c r="N35" s="113"/>
+      <c r="O35" s="112"/>
+      <c r="P35" s="113"/>
+      <c r="Q35" s="113"/>
+      <c r="S35" s="121"/>
+      <c r="T35" s="121"/>
+      <c r="U35" s="121"/>
+      <c r="V35" s="121"/>
+      <c r="W35" s="121"/>
+      <c r="X35" s="121"/>
+      <c r="Y35" s="121"/>
+      <c r="Z35" s="121"/>
+    </row>
+    <row r="36" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A36" s="109"/>
+      <c r="B36" s="111" t="s">
         <v>103</v>
       </c>
-      <c r="C36" s="117"/>
-      <c r="D36" s="117"/>
-      <c r="E36" s="116"/>
-      <c r="F36" s="119"/>
-      <c r="G36" s="119"/>
-      <c r="H36" s="119"/>
-      <c r="I36" s="119"/>
-      <c r="J36" s="119"/>
-      <c r="K36" s="119"/>
-      <c r="L36" s="119"/>
-      <c r="M36" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="N36" s="119"/>
-      <c r="O36" s="119"/>
-      <c r="P36" s="119"/>
-      <c r="Q36" s="119"/>
-      <c r="S36" s="127"/>
-      <c r="T36" s="127"/>
-      <c r="U36" s="127"/>
-      <c r="V36" s="127"/>
-      <c r="W36" s="127"/>
-      <c r="X36" s="127"/>
-      <c r="Y36" s="127"/>
-      <c r="Z36" s="127"/>
-    </row>
-    <row r="37" s="104" customFormat="1" ht="15" customHeight="1" spans="1:26">
-      <c r="A37" s="115"/>
-      <c r="B37" s="123" t="s">
+      <c r="C36" s="111"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="110"/>
+      <c r="F36" s="113"/>
+      <c r="G36" s="113"/>
+      <c r="H36" s="113"/>
+      <c r="I36" s="113"/>
+      <c r="J36" s="113"/>
+      <c r="K36" s="113"/>
+      <c r="L36" s="113"/>
+      <c r="M36" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="N36" s="113"/>
+      <c r="O36" s="113"/>
+      <c r="P36" s="113"/>
+      <c r="Q36" s="113"/>
+      <c r="S36" s="121"/>
+      <c r="T36" s="121"/>
+      <c r="U36" s="121"/>
+      <c r="V36" s="121"/>
+      <c r="W36" s="121"/>
+      <c r="X36" s="121"/>
+      <c r="Y36" s="121"/>
+      <c r="Z36" s="121"/>
+    </row>
+    <row r="37" s="98" customFormat="1" ht="15" customHeight="1" spans="1:26">
+      <c r="A37" s="109"/>
+      <c r="B37" s="117" t="s">
         <v>104</v>
       </c>
-      <c r="C37" s="124"/>
-      <c r="D37" s="125"/>
-      <c r="E37" s="116"/>
-      <c r="F37" s="119"/>
-      <c r="G37" s="119"/>
-      <c r="H37" s="119"/>
-      <c r="I37" s="119"/>
-      <c r="J37" s="119"/>
-      <c r="K37" s="119"/>
-      <c r="L37" s="119"/>
-      <c r="M37" s="119"/>
-      <c r="N37" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="O37" s="119"/>
-      <c r="P37" s="119"/>
-      <c r="Q37" s="119"/>
-      <c r="S37" s="127"/>
-      <c r="T37" s="127"/>
-      <c r="U37" s="127"/>
-      <c r="V37" s="127"/>
-      <c r="W37" s="127"/>
-      <c r="X37" s="127"/>
-      <c r="Y37" s="127"/>
-      <c r="Z37" s="127"/>
-    </row>
-    <row r="38" s="104" customFormat="1" ht="15" customHeight="1" spans="1:26">
-      <c r="A38" s="115"/>
-      <c r="B38" s="123" t="s">
+      <c r="C37" s="118"/>
+      <c r="D37" s="119"/>
+      <c r="E37" s="110"/>
+      <c r="F37" s="113"/>
+      <c r="G37" s="113"/>
+      <c r="H37" s="113"/>
+      <c r="I37" s="113"/>
+      <c r="J37" s="113"/>
+      <c r="K37" s="113"/>
+      <c r="L37" s="113"/>
+      <c r="M37" s="113"/>
+      <c r="N37" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="O37" s="113"/>
+      <c r="P37" s="113"/>
+      <c r="Q37" s="113"/>
+      <c r="S37" s="121"/>
+      <c r="T37" s="121"/>
+      <c r="U37" s="121"/>
+      <c r="V37" s="121"/>
+      <c r="W37" s="121"/>
+      <c r="X37" s="121"/>
+      <c r="Y37" s="121"/>
+      <c r="Z37" s="121"/>
+    </row>
+    <row r="38" s="98" customFormat="1" ht="15" customHeight="1" spans="1:26">
+      <c r="A38" s="109"/>
+      <c r="B38" s="117" t="s">
         <v>105</v>
       </c>
-      <c r="C38" s="124"/>
-      <c r="D38" s="125"/>
-      <c r="E38" s="116"/>
-      <c r="F38" s="119"/>
-      <c r="G38" s="119"/>
-      <c r="H38" s="119"/>
-      <c r="I38" s="119"/>
-      <c r="J38" s="119"/>
-      <c r="K38" s="119"/>
-      <c r="L38" s="119"/>
-      <c r="M38" s="119"/>
-      <c r="N38" s="119"/>
-      <c r="O38" s="119"/>
-      <c r="P38" s="119"/>
-      <c r="Q38" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="S38" s="127"/>
-      <c r="T38" s="127"/>
-      <c r="U38" s="127"/>
-      <c r="V38" s="127"/>
-      <c r="W38" s="127"/>
-      <c r="X38" s="127"/>
-      <c r="Y38" s="127"/>
-      <c r="Z38" s="127"/>
-    </row>
-    <row r="39" s="104" customFormat="1" ht="15" customHeight="1" spans="1:26">
-      <c r="A39" s="115" t="s">
+      <c r="C38" s="118"/>
+      <c r="D38" s="119"/>
+      <c r="E38" s="110"/>
+      <c r="F38" s="113"/>
+      <c r="G38" s="113"/>
+      <c r="H38" s="113"/>
+      <c r="I38" s="113"/>
+      <c r="J38" s="113"/>
+      <c r="K38" s="113"/>
+      <c r="L38" s="113"/>
+      <c r="M38" s="113"/>
+      <c r="N38" s="113"/>
+      <c r="O38" s="113"/>
+      <c r="P38" s="113"/>
+      <c r="Q38" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="S38" s="121"/>
+      <c r="T38" s="121"/>
+      <c r="U38" s="121"/>
+      <c r="V38" s="121"/>
+      <c r="W38" s="121"/>
+      <c r="X38" s="121"/>
+      <c r="Y38" s="121"/>
+      <c r="Z38" s="121"/>
+    </row>
+    <row r="39" s="98" customFormat="1" ht="15" customHeight="1" spans="1:26">
+      <c r="A39" s="109" t="s">
         <v>50</v>
       </c>
-      <c r="B39" s="105" t="s">
+      <c r="B39" s="99" t="s">
         <v>51</v>
       </c>
-      <c r="C39" s="105"/>
-      <c r="D39" s="105"/>
-      <c r="E39" s="116"/>
-      <c r="F39" s="116"/>
-      <c r="G39" s="116"/>
-      <c r="H39" s="116"/>
-      <c r="I39" s="116"/>
-      <c r="J39" s="116"/>
-      <c r="K39" s="116"/>
-      <c r="L39" s="116"/>
-      <c r="M39" s="116"/>
-      <c r="N39" s="116"/>
-      <c r="O39" s="116"/>
-      <c r="P39" s="116"/>
-      <c r="Q39" s="116"/>
-      <c r="S39" s="127"/>
-      <c r="T39" s="127"/>
-      <c r="U39" s="127"/>
-      <c r="V39" s="127"/>
-      <c r="W39" s="127"/>
-      <c r="X39" s="127"/>
-      <c r="Y39" s="127"/>
-      <c r="Z39" s="127"/>
-    </row>
-    <row r="40" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A40" s="115"/>
-      <c r="B40" s="117" t="s">
+      <c r="C39" s="99"/>
+      <c r="D39" s="99"/>
+      <c r="E39" s="110"/>
+      <c r="F39" s="110"/>
+      <c r="G39" s="110"/>
+      <c r="H39" s="110"/>
+      <c r="I39" s="110"/>
+      <c r="J39" s="110"/>
+      <c r="K39" s="110"/>
+      <c r="L39" s="110"/>
+      <c r="M39" s="110"/>
+      <c r="N39" s="110"/>
+      <c r="O39" s="110"/>
+      <c r="P39" s="110"/>
+      <c r="Q39" s="110"/>
+      <c r="S39" s="121"/>
+      <c r="T39" s="121"/>
+      <c r="U39" s="121"/>
+      <c r="V39" s="121"/>
+      <c r="W39" s="121"/>
+      <c r="X39" s="121"/>
+      <c r="Y39" s="121"/>
+      <c r="Z39" s="121"/>
+    </row>
+    <row r="40" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A40" s="109"/>
+      <c r="B40" s="111" t="s">
         <v>106</v>
       </c>
-      <c r="C40" s="117"/>
-      <c r="D40" s="117"/>
-      <c r="E40" s="118" t="s">
-        <v>30</v>
-      </c>
-      <c r="F40" s="116"/>
-      <c r="G40" s="116"/>
-      <c r="H40" s="116"/>
-      <c r="I40" s="116"/>
-      <c r="J40" s="116"/>
-      <c r="K40" s="116"/>
-      <c r="L40" s="116"/>
-      <c r="M40" s="116"/>
-      <c r="N40" s="116"/>
-      <c r="O40" s="116"/>
-      <c r="P40" s="116"/>
-      <c r="Q40" s="116"/>
-    </row>
-    <row r="41" s="104" customFormat="1" ht="15" customHeight="1" spans="1:26">
-      <c r="A41" s="115"/>
-      <c r="B41" s="117" t="s">
+      <c r="C40" s="111"/>
+      <c r="D40" s="111"/>
+      <c r="E40" s="112" t="s">
+        <v>30</v>
+      </c>
+      <c r="F40" s="110"/>
+      <c r="G40" s="110"/>
+      <c r="H40" s="110"/>
+      <c r="I40" s="110"/>
+      <c r="J40" s="110"/>
+      <c r="K40" s="110"/>
+      <c r="L40" s="110"/>
+      <c r="M40" s="110"/>
+      <c r="N40" s="110"/>
+      <c r="O40" s="110"/>
+      <c r="P40" s="110"/>
+      <c r="Q40" s="110"/>
+    </row>
+    <row r="41" s="98" customFormat="1" ht="15" customHeight="1" spans="1:26">
+      <c r="A41" s="109"/>
+      <c r="B41" s="111" t="s">
         <v>29</v>
       </c>
-      <c r="C41" s="117"/>
-      <c r="D41" s="117"/>
-      <c r="E41" s="116"/>
-      <c r="F41" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="G41" s="116"/>
-      <c r="H41" s="116"/>
-      <c r="I41" s="116"/>
-      <c r="J41" s="116"/>
-      <c r="K41" s="116"/>
-      <c r="L41" s="116"/>
-      <c r="M41" s="116"/>
-      <c r="N41" s="116"/>
-      <c r="O41" s="116"/>
-      <c r="P41" s="116"/>
-      <c r="Q41" s="116"/>
-    </row>
-    <row r="42" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A42" s="115"/>
-      <c r="B42" s="117" t="s">
+      <c r="C41" s="111"/>
+      <c r="D41" s="111"/>
+      <c r="E41" s="110"/>
+      <c r="F41" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="G41" s="110"/>
+      <c r="H41" s="110"/>
+      <c r="I41" s="110"/>
+      <c r="J41" s="110"/>
+      <c r="K41" s="110"/>
+      <c r="L41" s="110"/>
+      <c r="M41" s="110"/>
+      <c r="N41" s="110"/>
+      <c r="O41" s="110"/>
+      <c r="P41" s="110"/>
+      <c r="Q41" s="110"/>
+    </row>
+    <row r="42" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A42" s="109"/>
+      <c r="B42" s="111" t="s">
         <v>89</v>
       </c>
-      <c r="C42" s="117"/>
-      <c r="D42" s="117"/>
-      <c r="E42" s="116"/>
-      <c r="F42" s="116"/>
-      <c r="G42" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="H42" s="116"/>
-      <c r="I42" s="116"/>
-      <c r="J42" s="118"/>
-      <c r="K42" s="116"/>
-      <c r="L42" s="116"/>
-      <c r="M42" s="116"/>
-      <c r="N42" s="116"/>
-      <c r="O42" s="116"/>
-      <c r="P42" s="118"/>
-      <c r="Q42" s="118"/>
-    </row>
-    <row r="43" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A43" s="115"/>
-      <c r="B43" s="117" t="s">
+      <c r="C42" s="111"/>
+      <c r="D42" s="111"/>
+      <c r="E42" s="110"/>
+      <c r="F42" s="110"/>
+      <c r="G42" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="H42" s="110"/>
+      <c r="I42" s="110"/>
+      <c r="J42" s="112"/>
+      <c r="K42" s="110"/>
+      <c r="L42" s="110"/>
+      <c r="M42" s="110"/>
+      <c r="N42" s="110"/>
+      <c r="O42" s="110"/>
+      <c r="P42" s="112"/>
+      <c r="Q42" s="112"/>
+    </row>
+    <row r="43" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A43" s="109"/>
+      <c r="B43" s="111" t="s">
         <v>90</v>
       </c>
-      <c r="C43" s="117"/>
-      <c r="D43" s="117"/>
-      <c r="E43" s="116"/>
-      <c r="F43" s="116"/>
-      <c r="G43" s="116"/>
-      <c r="H43" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="I43" s="116"/>
-      <c r="J43" s="116"/>
-      <c r="K43" s="116"/>
-      <c r="L43" s="116"/>
-      <c r="M43" s="116"/>
-      <c r="N43" s="116"/>
-      <c r="O43" s="116"/>
-      <c r="P43" s="128" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q43" s="116"/>
-    </row>
-    <row r="44" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A44" s="115"/>
-      <c r="B44" s="117" t="s">
+      <c r="C43" s="111"/>
+      <c r="D43" s="111"/>
+      <c r="E43" s="110"/>
+      <c r="F43" s="110"/>
+      <c r="G43" s="110"/>
+      <c r="H43" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="I43" s="110"/>
+      <c r="J43" s="110"/>
+      <c r="K43" s="110"/>
+      <c r="L43" s="110"/>
+      <c r="M43" s="110"/>
+      <c r="N43" s="110"/>
+      <c r="O43" s="110"/>
+      <c r="P43" s="122" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q43" s="110"/>
+    </row>
+    <row r="44" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A44" s="109"/>
+      <c r="B44" s="111" t="s">
         <v>107</v>
       </c>
-      <c r="C44" s="117"/>
-      <c r="D44" s="117"/>
-      <c r="E44" s="116"/>
-      <c r="F44" s="116"/>
-      <c r="G44" s="116"/>
-      <c r="H44" s="116"/>
-      <c r="I44" s="118"/>
-      <c r="J44" s="116"/>
-      <c r="K44" s="118"/>
-      <c r="L44" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="M44" s="116"/>
-      <c r="N44" s="116"/>
-      <c r="O44" s="116"/>
-      <c r="P44" s="116"/>
-      <c r="Q44" s="129"/>
-    </row>
-    <row r="45" s="104" customFormat="1" ht="23.25" customHeight="1" spans="1:26">
-      <c r="A45" s="115"/>
-      <c r="B45" s="117" t="s">
+      <c r="C44" s="111"/>
+      <c r="D44" s="111"/>
+      <c r="E44" s="110"/>
+      <c r="F44" s="110"/>
+      <c r="G44" s="110"/>
+      <c r="H44" s="110"/>
+      <c r="I44" s="112"/>
+      <c r="J44" s="110"/>
+      <c r="K44" s="112"/>
+      <c r="L44" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="M44" s="110"/>
+      <c r="N44" s="110"/>
+      <c r="O44" s="110"/>
+      <c r="P44" s="110"/>
+      <c r="Q44" s="123"/>
+    </row>
+    <row r="45" s="98" customFormat="1" ht="23.25" customHeight="1" spans="1:26">
+      <c r="A45" s="109"/>
+      <c r="B45" s="111" t="s">
         <v>108</v>
       </c>
-      <c r="C45" s="117"/>
-      <c r="D45" s="117"/>
-      <c r="E45" s="116"/>
-      <c r="F45" s="116"/>
-      <c r="G45" s="116"/>
-      <c r="H45" s="116"/>
-      <c r="I45" s="116"/>
-      <c r="J45" s="116"/>
-      <c r="K45" s="116"/>
-      <c r="L45" s="116"/>
-      <c r="M45" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="N45" s="116"/>
-      <c r="O45" s="116"/>
-      <c r="P45" s="116"/>
-      <c r="Q45" s="129"/>
-    </row>
-    <row r="46" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A46" s="115"/>
-      <c r="B46" s="117" t="s">
+      <c r="C45" s="111"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="110"/>
+      <c r="F45" s="110"/>
+      <c r="G45" s="110"/>
+      <c r="H45" s="110"/>
+      <c r="I45" s="110"/>
+      <c r="J45" s="110"/>
+      <c r="K45" s="110"/>
+      <c r="L45" s="110"/>
+      <c r="M45" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="N45" s="110"/>
+      <c r="O45" s="110"/>
+      <c r="P45" s="110"/>
+      <c r="Q45" s="123"/>
+    </row>
+    <row r="46" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A46" s="109"/>
+      <c r="B46" s="111" t="s">
         <v>104</v>
       </c>
-      <c r="C46" s="117"/>
-      <c r="D46" s="117"/>
-      <c r="E46" s="116"/>
-      <c r="F46" s="116"/>
-      <c r="G46" s="116"/>
-      <c r="H46" s="116"/>
-      <c r="I46" s="116"/>
-      <c r="J46" s="116"/>
-      <c r="K46" s="116"/>
-      <c r="L46" s="118"/>
-      <c r="M46" s="116"/>
-      <c r="N46" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="O46" s="116"/>
-      <c r="P46" s="116"/>
-      <c r="Q46" s="129"/>
-    </row>
-    <row r="47" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A47" s="115"/>
-      <c r="B47" s="117" t="s">
+      <c r="C46" s="111"/>
+      <c r="D46" s="111"/>
+      <c r="E46" s="110"/>
+      <c r="F46" s="110"/>
+      <c r="G46" s="110"/>
+      <c r="H46" s="110"/>
+      <c r="I46" s="110"/>
+      <c r="J46" s="110"/>
+      <c r="K46" s="110"/>
+      <c r="L46" s="112"/>
+      <c r="M46" s="110"/>
+      <c r="N46" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="O46" s="110"/>
+      <c r="P46" s="110"/>
+      <c r="Q46" s="123"/>
+    </row>
+    <row r="47" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A47" s="109"/>
+      <c r="B47" s="111" t="s">
         <v>96</v>
       </c>
-      <c r="C47" s="117"/>
-      <c r="D47" s="117"/>
-      <c r="E47" s="116"/>
-      <c r="F47" s="116"/>
-      <c r="G47" s="116"/>
-      <c r="H47" s="116"/>
-      <c r="I47" s="116"/>
-      <c r="J47" s="116"/>
-      <c r="K47" s="116"/>
-      <c r="L47" s="116"/>
-      <c r="M47" s="118"/>
-      <c r="N47" s="116"/>
-      <c r="O47" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="P47" s="116"/>
-      <c r="Q47" s="129"/>
-    </row>
-    <row r="48" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A48" s="115"/>
-      <c r="B48" s="117" t="s">
+      <c r="C47" s="111"/>
+      <c r="D47" s="111"/>
+      <c r="E47" s="110"/>
+      <c r="F47" s="110"/>
+      <c r="G47" s="110"/>
+      <c r="H47" s="110"/>
+      <c r="I47" s="110"/>
+      <c r="J47" s="110"/>
+      <c r="K47" s="110"/>
+      <c r="L47" s="110"/>
+      <c r="M47" s="112"/>
+      <c r="N47" s="110"/>
+      <c r="O47" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="P47" s="110"/>
+      <c r="Q47" s="123"/>
+    </row>
+    <row r="48" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A48" s="109"/>
+      <c r="B48" s="111" t="s">
         <v>31</v>
       </c>
-      <c r="C48" s="117"/>
-      <c r="D48" s="117"/>
-      <c r="E48" s="116"/>
-      <c r="F48" s="116"/>
-      <c r="G48" s="116"/>
-      <c r="H48" s="116"/>
-      <c r="I48" s="116"/>
-      <c r="J48" s="116"/>
-      <c r="K48" s="116"/>
-      <c r="L48" s="116"/>
-      <c r="M48" s="116"/>
-      <c r="N48" s="118"/>
-      <c r="O48" s="116"/>
-      <c r="Q48" s="119" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="49" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
-      <c r="A49" s="115"/>
-      <c r="B49" s="105" t="s">
+      <c r="C48" s="111"/>
+      <c r="D48" s="111"/>
+      <c r="E48" s="110"/>
+      <c r="F48" s="110"/>
+      <c r="G48" s="110"/>
+      <c r="H48" s="110"/>
+      <c r="I48" s="110"/>
+      <c r="J48" s="110"/>
+      <c r="K48" s="110"/>
+      <c r="L48" s="110"/>
+      <c r="M48" s="110"/>
+      <c r="N48" s="112"/>
+      <c r="O48" s="110"/>
+      <c r="Q48" s="113" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
+      <c r="A49" s="109"/>
+      <c r="B49" s="99" t="s">
         <v>55</v>
       </c>
-      <c r="C49" s="105"/>
-      <c r="D49" s="105"/>
-      <c r="E49" s="116"/>
-      <c r="F49" s="116"/>
-      <c r="G49" s="116"/>
-      <c r="H49" s="116"/>
-      <c r="I49" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="J49" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="K49" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="M49" s="116"/>
-      <c r="N49" s="116"/>
-      <c r="O49" s="116"/>
-      <c r="P49" s="116"/>
-      <c r="Q49" s="116"/>
-    </row>
-    <row r="50" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
-      <c r="A50" s="115"/>
-      <c r="B50" s="117"/>
-      <c r="C50" s="117"/>
-      <c r="D50" s="117"/>
-      <c r="E50" s="116"/>
-      <c r="F50" s="116"/>
-      <c r="G50" s="116"/>
-      <c r="H50" s="116"/>
-      <c r="I50" s="116"/>
-      <c r="J50" s="116"/>
-      <c r="K50" s="116"/>
-      <c r="L50" s="116"/>
-      <c r="M50" s="116"/>
-      <c r="N50" s="116"/>
-      <c r="O50" s="116"/>
-      <c r="P50" s="116"/>
-      <c r="Q50" s="116"/>
-    </row>
-    <row r="51" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
-      <c r="A51" s="115" t="s">
+      <c r="C49" s="99"/>
+      <c r="D49" s="99"/>
+      <c r="E49" s="110"/>
+      <c r="F49" s="110"/>
+      <c r="G49" s="110"/>
+      <c r="H49" s="110"/>
+      <c r="I49" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="J49" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="K49" s="113" t="s">
+        <v>30</v>
+      </c>
+      <c r="M49" s="110"/>
+      <c r="N49" s="110"/>
+      <c r="O49" s="110"/>
+      <c r="P49" s="110"/>
+      <c r="Q49" s="110"/>
+    </row>
+    <row r="50" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
+      <c r="A50" s="109"/>
+      <c r="B50" s="111"/>
+      <c r="C50" s="111"/>
+      <c r="D50" s="111"/>
+      <c r="E50" s="110"/>
+      <c r="F50" s="110"/>
+      <c r="G50" s="110"/>
+      <c r="H50" s="110"/>
+      <c r="I50" s="110"/>
+      <c r="J50" s="110"/>
+      <c r="K50" s="110"/>
+      <c r="L50" s="110"/>
+      <c r="M50" s="110"/>
+      <c r="N50" s="110"/>
+      <c r="O50" s="110"/>
+      <c r="P50" s="110"/>
+      <c r="Q50" s="110"/>
+    </row>
+    <row r="51" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
+      <c r="A51" s="109" t="s">
         <v>109</v>
       </c>
-      <c r="B51" s="130" t="s">
+      <c r="B51" s="124" t="s">
         <v>56</v>
       </c>
-      <c r="C51" s="130"/>
-      <c r="D51" s="130"/>
-      <c r="E51" s="116" t="s">
+      <c r="C51" s="124"/>
+      <c r="D51" s="124"/>
+      <c r="E51" s="110" t="s">
         <v>57</v>
       </c>
-      <c r="F51" s="116" t="s">
+      <c r="F51" s="110" t="s">
         <v>57</v>
       </c>
-      <c r="G51" s="116" t="s">
+      <c r="G51" s="110" t="s">
         <v>57</v>
       </c>
-      <c r="H51" s="116" t="s">
+      <c r="H51" s="110" t="s">
         <v>57</v>
       </c>
-      <c r="I51" s="116" t="s">
+      <c r="I51" s="110" t="s">
         <v>110</v>
       </c>
-      <c r="J51" s="116" t="s">
+      <c r="J51" s="110" t="s">
         <v>110</v>
       </c>
-      <c r="K51" s="116" t="s">
+      <c r="K51" s="110" t="s">
         <v>110</v>
       </c>
-      <c r="L51" s="116" t="s">
+      <c r="L51" s="110" t="s">
         <v>58</v>
       </c>
-      <c r="M51" s="116" t="s">
+      <c r="M51" s="110" t="s">
         <v>58</v>
       </c>
-      <c r="N51" s="116" t="s">
+      <c r="N51" s="110" t="s">
         <v>58</v>
       </c>
-      <c r="O51" s="116" t="s">
+      <c r="O51" s="110" t="s">
         <v>58</v>
       </c>
-      <c r="P51" s="116" t="s">
+      <c r="P51" s="110" t="s">
         <v>58</v>
       </c>
-      <c r="Q51" s="116" t="s">
+      <c r="Q51" s="110" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="52" s="104" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
-      <c r="A52" s="115"/>
-      <c r="B52" s="110" t="s">
+    <row r="52" s="98" customFormat="1" ht="15.75" customHeight="1" spans="1:17">
+      <c r="A52" s="109"/>
+      <c r="B52" s="104" t="s">
         <v>59</v>
       </c>
-      <c r="C52" s="110"/>
-      <c r="D52" s="110"/>
-      <c r="E52" s="131" t="s">
+      <c r="C52" s="104"/>
+      <c r="D52" s="104"/>
+      <c r="E52" s="125" t="s">
         <v>61</v>
       </c>
-      <c r="F52" s="131" t="s">
+      <c r="F52" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="G52" s="131" t="s">
+      <c r="G52" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="H52" s="131" t="s">
+      <c r="H52" s="125" t="s">
         <v>61</v>
       </c>
-      <c r="I52" s="131" t="s">
+      <c r="I52" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="J52" s="131" t="s">
+      <c r="J52" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="K52" s="131" t="s">
+      <c r="K52" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="L52" s="131" t="s">
+      <c r="L52" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="M52" s="131" t="s">
+      <c r="M52" s="125" t="s">
         <v>61</v>
       </c>
-      <c r="N52" s="131" t="s">
+      <c r="N52" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="O52" s="131" t="s">
+      <c r="O52" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="P52" s="131" t="s">
+      <c r="P52" s="125" t="s">
         <v>61</v>
       </c>
-      <c r="Q52" s="131" t="s">
+      <c r="Q52" s="125" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="53" s="104" customFormat="1" spans="1:17">
-      <c r="A53" s="115"/>
-      <c r="B53" s="110" t="s">
+    <row r="53" s="98" customFormat="1" spans="1:17">
+      <c r="A53" s="109"/>
+      <c r="B53" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="C53" s="110"/>
-      <c r="D53" s="110"/>
-      <c r="E53" s="132" t="s">
+      <c r="C53" s="104"/>
+      <c r="D53" s="104"/>
+      <c r="E53" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="F53" s="132" t="s">
+      <c r="F53" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="G53" s="132" t="s">
+      <c r="G53" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="H53" s="132" t="s">
+      <c r="H53" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="I53" s="132" t="s">
+      <c r="I53" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="J53" s="132" t="s">
+      <c r="J53" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="K53" s="132" t="s">
+      <c r="K53" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="L53" s="132" t="s">
+      <c r="L53" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="M53" s="132" t="s">
+      <c r="M53" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="N53" s="132" t="s">
+      <c r="N53" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="O53" s="132" t="s">
+      <c r="O53" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="P53" s="132" t="s">
+      <c r="P53" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="Q53" s="132" t="s">
+      <c r="Q53" s="126" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="54" s="104" customFormat="1" ht="30" customHeight="1" spans="1:17">
-      <c r="A54" s="115"/>
-      <c r="B54" s="110" t="s">
+    <row r="54" s="98" customFormat="1" ht="30" customHeight="1" spans="1:17">
+      <c r="A54" s="109"/>
+      <c r="B54" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="C54" s="110"/>
-      <c r="D54" s="110"/>
-      <c r="E54" s="116"/>
-      <c r="F54" s="133" t="s">
+      <c r="C54" s="104"/>
+      <c r="D54" s="104"/>
+      <c r="E54" s="110"/>
+      <c r="F54" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="G54" s="133" t="s">
+      <c r="G54" s="127" t="s">
         <v>66</v>
       </c>
-      <c r="H54" s="116"/>
-      <c r="I54" s="134" t="s">
+      <c r="H54" s="110"/>
+      <c r="I54" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="J54" s="133" t="s">
+      <c r="J54" s="127" t="s">
         <v>68</v>
       </c>
-      <c r="K54" s="134" t="s">
+      <c r="K54" s="128" t="s">
         <v>69</v>
       </c>
-      <c r="L54" s="133" t="s">
+      <c r="L54" s="127" t="s">
         <v>70</v>
       </c>
-      <c r="M54" s="116"/>
-      <c r="N54" s="133" t="s">
+      <c r="M54" s="110"/>
+      <c r="N54" s="127" t="s">
         <v>71</v>
       </c>
-      <c r="O54" s="134" t="s">
+      <c r="O54" s="128" t="s">
         <v>72</v>
       </c>
-      <c r="P54" s="133"/>
-      <c r="Q54" s="133" t="s">
+      <c r="P54" s="127"/>
+      <c r="Q54" s="127" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="57" s="104" customFormat="1" spans="1:17">
-      <c r="B57" s="135" t="s">
+    <row r="57" s="98" customFormat="1" spans="1:17">
+      <c r="B57" s="129" t="s">
         <v>76</v>
       </c>
-      <c r="C57" s="136"/>
-    </row>
-    <row r="58" s="104" customFormat="1" spans="1:17">
-      <c r="B58" s="135" t="s">
+      <c r="C57" s="130"/>
+    </row>
+    <row r="58" s="98" customFormat="1" spans="1:17">
+      <c r="B58" s="129" t="s">
         <v>63</v>
       </c>
-      <c r="C58" s="137">
+      <c r="C58" s="131">
         <v>46063</v>
       </c>
     </row>
-    <row r="59" s="104" customFormat="1" spans="1:17">
-      <c r="B59" s="104" t="s">
+    <row r="59" s="98" customFormat="1" spans="1:17">
+      <c r="B59" s="98" t="s">
         <v>65</v>
       </c>
-      <c r="C59" s="104" t="s">
+      <c r="C59" s="98" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="60" s="104" customFormat="1" spans="1:17">
-      <c r="B60" s="104" t="s">
+    <row r="60" s="98" customFormat="1" spans="1:17">
+      <c r="B60" s="98" t="s">
         <v>66</v>
       </c>
-      <c r="C60" s="104" t="s">
+      <c r="C60" s="98" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="61" s="104" customFormat="1" spans="1:17">
-      <c r="B61" s="104" t="s">
+    <row r="61" s="98" customFormat="1" spans="1:17">
+      <c r="B61" s="98" t="s">
         <v>67</v>
       </c>
-      <c r="C61" s="104" t="s">
+      <c r="C61" s="98" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="62" s="104" customFormat="1" spans="1:17">
-      <c r="B62" s="104" t="s">
+    <row r="62" s="98" customFormat="1" spans="1:17">
+      <c r="B62" s="98" t="s">
         <v>68</v>
       </c>
-      <c r="C62" s="104" t="s">
+      <c r="C62" s="98" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="63" s="104" customFormat="1" spans="1:17">
-      <c r="B63" s="104" t="s">
+    <row r="63" s="98" customFormat="1" spans="1:17">
+      <c r="B63" s="98" t="s">
         <v>69</v>
       </c>
-      <c r="C63" s="104" t="s">
+      <c r="C63" s="98" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="64" s="104" customFormat="1" spans="1:17">
-      <c r="B64" s="104" t="s">
+    <row r="64" s="98" customFormat="1" spans="1:17">
+      <c r="B64" s="98" t="s">
         <v>70</v>
       </c>
-      <c r="C64" s="138" t="s">
+      <c r="C64" s="132" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="65" customFormat="1" ht="14.4" spans="2:3">
-      <c r="B65" s="104" t="s">
+      <c r="B65" s="98" t="s">
         <v>71</v>
       </c>
-      <c r="C65" s="104" t="s">
+      <c r="C65" s="98" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="66" spans="2:3">
-      <c r="B66" s="104" t="s">
+      <c r="B66" s="98" t="s">
         <v>72</v>
       </c>
-      <c r="C66" s="104" t="s">
+      <c r="C66" s="98" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="67" spans="2:3">
-      <c r="B67" s="104" t="s">
+      <c r="B67" s="98" t="s">
         <v>73</v>
       </c>
-      <c r="C67" s="104" t="s">
+      <c r="C67" s="98" t="s">
         <v>118</v>
       </c>
     </row>
@@ -6301,7 +6198,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V36"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8.22222222222222" style="1" customWidth="1"/>
@@ -6309,21 +6206,23 @@
     <col min="3" max="3" width="13" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.3333333333333" style="3" customWidth="1"/>
     <col min="5" max="5" width="1.77777777777778" style="1" hidden="1" customWidth="1"/>
-    <col min="6" max="21" width="2.88888888888889" style="1" customWidth="1"/>
-    <col min="22" max="23" width="9" style="1"/>
-    <col min="24" max="24" width="23.3333333333333" style="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7777777777778" style="1" customWidth="1"/>
-    <col min="26" max="26" width="16.2222222222222" style="1" customWidth="1"/>
-    <col min="27" max="27" width="14.4444444444444" style="1" customWidth="1"/>
-    <col min="28" max="28" width="16" style="1" customWidth="1"/>
-    <col min="29" max="16384" width="9" style="1"/>
+    <col min="6" max="12" width="2.88888888888889" style="1" customWidth="1"/>
+    <col min="13" max="13" width="11.8888888888889" style="1" customWidth="1"/>
+    <col min="14" max="20" width="2.88888888888889" style="1" customWidth="1"/>
+    <col min="21" max="22" width="9" style="1"/>
+    <col min="23" max="23" width="23.3333333333333" style="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7777777777778" style="1" customWidth="1"/>
+    <col min="25" max="25" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="26" max="26" width="14.4444444444444" style="1" customWidth="1"/>
+    <col min="27" max="27" width="16" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" customHeight="1" spans="1:22">
+    <row r="1" s="1" customFormat="1" ht="12" customHeight="1" spans="1:21">
       <c r="B1" s="2"/>
       <c r="D1" s="4"/>
     </row>
-    <row r="2" s="1" customFormat="1" ht="15" customHeight="1" spans="1:22">
+    <row r="2" s="1" customFormat="1" ht="15" customHeight="1" spans="1:21">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -6338,20 +6237,19 @@
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="7" t="s">
+      <c r="K2" s="7" t="s">
         <v>119</v>
       </c>
+      <c r="L2" s="10"/>
       <c r="M2" s="10"/>
       <c r="N2" s="10"/>
       <c r="O2" s="10"/>
       <c r="P2" s="10"/>
       <c r="Q2" s="10"/>
       <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="11"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:22">
+      <c r="S2" s="11"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A3" s="12" t="s">
         <v>2</v>
       </c>
@@ -6367,23 +6265,22 @@
       <c r="G3" s="18"/>
       <c r="H3" s="18"/>
       <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="20" t="s">
-        <v>120</v>
-      </c>
+      <c r="J3" s="19"/>
+      <c r="K3" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="L3" s="20"/>
       <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
+      <c r="N3" s="21"/>
       <c r="O3" s="21"/>
       <c r="P3" s="21"/>
       <c r="Q3" s="21"/>
       <c r="R3" s="21"/>
-      <c r="S3" s="21"/>
-      <c r="T3" s="22"/>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:22">
+      <c r="S3" s="22"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A4" s="23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B4" s="24"/>
       <c r="C4" s="25"/>
@@ -6395,26 +6292,25 @@
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="31"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="32"/>
       <c r="M4" s="32"/>
       <c r="N4" s="32"/>
       <c r="O4" s="32"/>
       <c r="P4" s="32"/>
       <c r="Q4" s="32"/>
       <c r="R4" s="32"/>
-      <c r="S4" s="32"/>
-      <c r="T4" s="33"/>
-      <c r="V4" s="34"/>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:22">
+      <c r="S4" s="33"/>
+      <c r="U4" s="34"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A5" s="23" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="24"/>
       <c r="C5" s="35" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D5" s="35"/>
       <c r="E5" s="35"/>
@@ -6423,7 +6319,7 @@
       <c r="H5" s="36"/>
       <c r="I5" s="36"/>
       <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
+      <c r="K5" s="35"/>
       <c r="L5" s="35"/>
       <c r="M5" s="35"/>
       <c r="N5" s="35"/>
@@ -6432,9 +6328,8 @@
       <c r="Q5" s="35"/>
       <c r="R5" s="35"/>
       <c r="S5" s="35"/>
-      <c r="T5" s="35"/>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:22">
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A6" s="37" t="s">
         <v>9</v>
       </c>
@@ -6450,69 +6345,67 @@
       <c r="G6" s="40"/>
       <c r="H6" s="40"/>
       <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="40" t="s">
+      <c r="J6" s="42"/>
+      <c r="K6" s="40" t="s">
         <v>12</v>
       </c>
+      <c r="L6" s="40"/>
       <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="43" t="s">
+      <c r="N6" s="43" t="s">
         <v>13</v>
       </c>
+      <c r="O6" s="40"/>
       <c r="P6" s="40"/>
       <c r="Q6" s="40"/>
       <c r="R6" s="40"/>
-      <c r="S6" s="40"/>
-      <c r="T6" s="44"/>
-      <c r="V6" s="34"/>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:22">
+      <c r="S6" s="44"/>
+      <c r="U6" s="34"/>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A7" s="45">
-        <f>COUNTIF(F28:HQ28,"P")</f>
-        <v>1</v>
+        <f>COUNTIF(F19:HP19,"P")</f>
+        <v>2</v>
       </c>
       <c r="B7" s="46"/>
       <c r="C7" s="47">
-        <f>COUNTIF(F28:HQ28,"F")</f>
-        <v>2</v>
+        <f>COUNTIF(F19:HP19,"F")</f>
+        <v>0</v>
       </c>
       <c r="D7" s="48"/>
       <c r="E7" s="46"/>
       <c r="F7" s="47">
-        <f>SUM(O7,-A7,-C7)</f>
+        <f>SUM(N7,-A7,-C7)</f>
         <v>0</v>
       </c>
       <c r="G7" s="48"/>
       <c r="H7" s="48"/>
       <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="49"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="50">
+        <f>COUNTIF(E18:HP18,"N")</f>
+        <v>2</v>
+      </c>
       <c r="L7" s="50">
-        <f>COUNTIF(E27:HQ27,"N")</f>
-        <v>3</v>
+        <f>COUNTIF(E18:HP18,"A")</f>
+        <v>0</v>
       </c>
       <c r="M7" s="50">
-        <f>COUNTIF(E27:HQ27,"A")</f>
+        <f>COUNTIF(E18:HP18,"B")</f>
         <v>0</v>
       </c>
       <c r="N7" s="50">
-        <f>COUNTIF(E27:HQ27,"B")</f>
-        <v>0</v>
-      </c>
-      <c r="O7" s="50">
-        <f>COUNTA(E9:HT9)</f>
-        <v>3</v>
-      </c>
+        <f>COUNTA(E9:HS9)</f>
+        <v>2</v>
+      </c>
+      <c r="O7" s="48"/>
       <c r="P7" s="48"/>
       <c r="Q7" s="48"/>
       <c r="R7" s="48"/>
-      <c r="S7" s="48"/>
-      <c r="T7" s="51"/>
-      <c r="U7" s="52"/>
+      <c r="S7" s="51"/>
+      <c r="T7" s="52"/>
     </row>
     <row r="8"/>
-    <row r="9" s="1" customFormat="1" ht="51.95" spans="1:22">
+    <row r="9" s="1" customFormat="1" ht="51.95" spans="1:21">
       <c r="A9" s="53"/>
       <c r="B9" s="54"/>
       <c r="C9" s="55"/>
@@ -6524,9 +6417,7 @@
       <c r="G9" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="57" t="s">
-        <v>16</v>
-      </c>
+      <c r="I9" s="58"/>
       <c r="J9" s="58"/>
       <c r="K9" s="58"/>
       <c r="L9" s="58"/>
@@ -6537,24 +6428,23 @@
       <c r="Q9" s="58"/>
       <c r="R9" s="58"/>
       <c r="S9" s="58"/>
-      <c r="T9" s="58"/>
-      <c r="U9" s="59"/>
-      <c r="V9" s="34"/>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:22">
+      <c r="T9" s="59"/>
+      <c r="U9" s="34"/>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A10" s="60" t="s">
         <v>27</v>
       </c>
       <c r="B10" s="61" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C10" s="62"/>
       <c r="D10" s="63"/>
       <c r="E10" s="64"/>
       <c r="F10" s="65"/>
       <c r="G10" s="65"/>
-      <c r="H10" s="65"/>
-      <c r="I10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="66"/>
       <c r="J10" s="66"/>
       <c r="K10" s="66"/>
       <c r="L10" s="66"/>
@@ -6565,21 +6455,20 @@
       <c r="Q10" s="66"/>
       <c r="R10" s="66"/>
       <c r="S10" s="66"/>
-      <c r="T10" s="66"/>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:22">
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A11" s="67"/>
       <c r="B11" s="61"/>
       <c r="C11" s="62"/>
       <c r="D11" s="63">
-        <v>-1</v>
+        <v>110</v>
       </c>
       <c r="E11" s="68"/>
       <c r="F11" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="70"/>
-      <c r="H11" s="65"/>
+      <c r="G11" s="69"/>
+      <c r="I11" s="66"/>
       <c r="J11" s="66"/>
       <c r="K11" s="66"/>
       <c r="L11" s="66"/>
@@ -6590,22 +6479,21 @@
       <c r="Q11" s="66"/>
       <c r="R11" s="66"/>
       <c r="S11" s="66"/>
-      <c r="T11" s="66"/>
-      <c r="V11" s="34"/>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:22">
+      <c r="U11" s="34"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A12" s="67"/>
       <c r="B12" s="61"/>
       <c r="C12" s="62"/>
-      <c r="D12" s="63">
-        <v>0</v>
+      <c r="D12" s="63" t="s">
+        <v>123</v>
       </c>
       <c r="E12" s="68"/>
       <c r="F12" s="65"/>
       <c r="G12" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="H12" s="65"/>
+      <c r="I12" s="66"/>
       <c r="J12" s="66"/>
       <c r="K12" s="66"/>
       <c r="L12" s="66"/>
@@ -6616,21 +6504,20 @@
       <c r="Q12" s="66"/>
       <c r="R12" s="66"/>
       <c r="S12" s="66"/>
-      <c r="T12" s="66"/>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A13" s="67"/>
-      <c r="B13" s="61"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="63">
-        <v>5</v>
-      </c>
-      <c r="E13" s="71"/>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:21">
+      <c r="A13" s="70" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="71" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="72"/>
+      <c r="D13" s="73"/>
+      <c r="E13" s="74"/>
       <c r="F13" s="65"/>
       <c r="G13" s="65"/>
-      <c r="H13" s="70" t="s">
-        <v>30</v>
-      </c>
+      <c r="I13" s="66"/>
       <c r="J13" s="66"/>
       <c r="K13" s="66"/>
       <c r="L13" s="66"/>
@@ -6641,22 +6528,21 @@
       <c r="Q13" s="66"/>
       <c r="R13" s="66"/>
       <c r="S13" s="66"/>
-      <c r="T13" s="66"/>
-      <c r="V13" s="34"/>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A14" s="72" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="73" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="74"/>
-      <c r="D14" s="75"/>
-      <c r="E14" s="76"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="65"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:21">
+      <c r="A14" s="75"/>
+      <c r="B14" s="76"/>
+      <c r="C14" s="77"/>
+      <c r="D14" s="78">
+        <v>6</v>
+      </c>
+      <c r="E14" s="79"/>
+      <c r="F14" s="69" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="69"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="66"/>
       <c r="J14" s="66"/>
       <c r="K14" s="66"/>
       <c r="L14" s="66"/>
@@ -6667,20 +6553,17 @@
       <c r="Q14" s="66"/>
       <c r="R14" s="66"/>
       <c r="S14" s="66"/>
-      <c r="T14" s="66"/>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A15" s="77"/>
-      <c r="B15" s="78" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="79"/>
-      <c r="D15" s="80"/>
-      <c r="E15" s="81"/>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="1"/>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:21">
+      <c r="A15" s="75"/>
+      <c r="B15" s="76"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="78"/>
+      <c r="E15" s="79"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="66"/>
       <c r="J15" s="66"/>
       <c r="K15" s="66"/>
       <c r="L15" s="66"/>
@@ -6691,24 +6574,17 @@
       <c r="Q15" s="66"/>
       <c r="R15" s="66"/>
       <c r="S15" s="66"/>
-      <c r="T15" s="66"/>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A16" s="77"/>
-      <c r="B16" s="78"/>
-      <c r="C16" s="79"/>
-      <c r="D16" s="80">
-        <v>1</v>
-      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:21">
+      <c r="A16" s="75"/>
+      <c r="B16" s="76"/>
+      <c r="C16" s="80"/>
+      <c r="D16" s="78"/>
       <c r="E16" s="81"/>
-      <c r="F16" s="69" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="70" t="s">
-        <v>30</v>
-      </c>
-      <c r="H16" s="70"/>
-      <c r="I16" s="1"/>
+      <c r="F16" s="65"/>
+      <c r="G16" s="65"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="66"/>
       <c r="J16" s="66"/>
       <c r="K16" s="66"/>
       <c r="L16" s="66"/>
@@ -6719,22 +6595,21 @@
       <c r="Q16" s="66"/>
       <c r="R16" s="66"/>
       <c r="S16" s="66"/>
-      <c r="T16" s="66"/>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A17" s="77"/>
-      <c r="B17" s="78"/>
-      <c r="C17" s="79"/>
-      <c r="D17" s="80">
-        <v>6</v>
-      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:19">
+      <c r="A17" s="75"/>
+      <c r="B17" s="76" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="80"/>
+      <c r="D17" s="78"/>
       <c r="E17" s="81"/>
-      <c r="F17" s="70"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="69" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="1"/>
+      <c r="F17" s="65"/>
+      <c r="G17" s="69" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" s="1"/>
+      <c r="I17" s="66"/>
       <c r="J17" s="66"/>
       <c r="K17" s="66"/>
       <c r="L17" s="66"/>
@@ -6745,419 +6620,172 @@
       <c r="Q17" s="66"/>
       <c r="R17" s="66"/>
       <c r="S17" s="66"/>
-      <c r="T17" s="66"/>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A18" s="77"/>
-      <c r="B18" s="78" t="s">
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:19">
+      <c r="A18" s="70" t="s">
+        <v>109</v>
+      </c>
+      <c r="B18" s="82" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="82"/>
+      <c r="D18" s="82"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="G18" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="H18" s="1"/>
+      <c r="I18" s="85"/>
+      <c r="J18" s="85"/>
+      <c r="K18" s="85"/>
+      <c r="L18" s="85"/>
+      <c r="M18" s="85"/>
+      <c r="N18" s="85"/>
+      <c r="O18" s="85"/>
+      <c r="P18" s="85"/>
+      <c r="Q18" s="85"/>
+      <c r="R18" s="85"/>
+      <c r="S18" s="85"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:19">
+      <c r="A19" s="75"/>
+      <c r="B19" s="86" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="86"/>
+      <c r="D19" s="86"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="88" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19" s="88" t="s">
+        <v>61</v>
+      </c>
+      <c r="H19" s="1"/>
+      <c r="I19" s="85"/>
+      <c r="J19" s="85"/>
+      <c r="K19" s="85"/>
+      <c r="L19" s="85"/>
+      <c r="M19" s="85"/>
+      <c r="N19" s="85"/>
+      <c r="O19" s="85"/>
+      <c r="P19" s="85"/>
+      <c r="Q19" s="85"/>
+      <c r="R19" s="85"/>
+      <c r="S19" s="85"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:19">
+      <c r="A20" s="75"/>
+      <c r="B20" s="86" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="86"/>
+      <c r="D20" s="86"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="90" t="s">
+        <v>63</v>
+      </c>
+      <c r="G20" s="90" t="s">
+        <v>63</v>
+      </c>
+      <c r="H20" s="1"/>
+      <c r="I20" s="91"/>
+      <c r="J20" s="91"/>
+      <c r="K20" s="91"/>
+      <c r="L20" s="91"/>
+      <c r="M20" s="91"/>
+      <c r="N20" s="91"/>
+      <c r="O20" s="91"/>
+      <c r="P20" s="91"/>
+      <c r="Q20" s="91"/>
+      <c r="R20" s="91"/>
+      <c r="S20" s="91"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:19">
+      <c r="A21" s="92"/>
+      <c r="B21" s="93" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="93"/>
+      <c r="D21" s="93"/>
+      <c r="E21" s="94"/>
+      <c r="F21" s="95"/>
+      <c r="G21" s="95"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="96"/>
+      <c r="J21" s="96"/>
+      <c r="K21" s="96"/>
+      <c r="L21" s="96"/>
+      <c r="M21" s="96"/>
+      <c r="N21" s="96"/>
+      <c r="O21" s="96"/>
+      <c r="P21" s="96"/>
+      <c r="Q21" s="96"/>
+      <c r="R21" s="96"/>
+      <c r="S21" s="96"/>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="13.95" spans="1:19">
+      <c r="A22" s="2"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:19">
+      <c r="B24" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C18" s="79"/>
-      <c r="D18" s="80"/>
-      <c r="E18" s="81"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="69"/>
-      <c r="H18" s="69"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="66"/>
-      <c r="K18" s="66"/>
-      <c r="L18" s="66"/>
-      <c r="M18" s="66"/>
-      <c r="N18" s="66"/>
-      <c r="O18" s="66"/>
-      <c r="P18" s="66"/>
-      <c r="Q18" s="66"/>
-      <c r="R18" s="66"/>
-      <c r="S18" s="66"/>
-      <c r="T18" s="66"/>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A19" s="77"/>
-      <c r="B19" s="78"/>
-      <c r="C19" s="79"/>
-      <c r="D19" s="80">
-        <v>1</v>
-      </c>
-      <c r="E19" s="81"/>
-      <c r="F19" s="69" t="s">
-        <v>30</v>
-      </c>
-      <c r="G19" s="70" t="s">
-        <v>30</v>
-      </c>
-      <c r="H19" s="70"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="66"/>
-      <c r="K19" s="66"/>
-      <c r="L19" s="66"/>
-      <c r="M19" s="66"/>
-      <c r="N19" s="66"/>
-      <c r="O19" s="66"/>
-      <c r="P19" s="66"/>
-      <c r="Q19" s="66"/>
-      <c r="R19" s="66"/>
-      <c r="S19" s="66"/>
-      <c r="T19" s="66"/>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A20" s="77"/>
-      <c r="B20" s="78"/>
-      <c r="C20" s="79"/>
-      <c r="D20" s="80">
-        <v>3</v>
-      </c>
-      <c r="E20" s="81"/>
-      <c r="F20" s="70"/>
-      <c r="G20" s="69"/>
-      <c r="H20" s="69" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="1"/>
-      <c r="J20" s="66"/>
-      <c r="K20" s="66"/>
-      <c r="L20" s="66"/>
-      <c r="M20" s="66"/>
-      <c r="N20" s="66"/>
-      <c r="O20" s="66"/>
-      <c r="P20" s="66"/>
-      <c r="Q20" s="66"/>
-      <c r="R20" s="66"/>
-      <c r="S20" s="66"/>
-      <c r="T20" s="66"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A21" s="77"/>
-      <c r="B21" s="78"/>
-      <c r="C21" s="82"/>
-      <c r="D21" s="80"/>
-      <c r="E21" s="83"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="65"/>
-      <c r="H21" s="65"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="66"/>
-      <c r="K21" s="66"/>
-      <c r="L21" s="66"/>
-      <c r="M21" s="66"/>
-      <c r="N21" s="66"/>
-      <c r="O21" s="66"/>
-      <c r="P21" s="66"/>
-      <c r="Q21" s="66"/>
-      <c r="R21" s="66"/>
-      <c r="S21" s="66"/>
-      <c r="T21" s="66"/>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A22" s="77"/>
-      <c r="B22" s="78" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" s="82"/>
-      <c r="D22" s="80"/>
-      <c r="E22" s="83"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="65"/>
-      <c r="H22" s="65"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="66"/>
-      <c r="K22" s="66"/>
-      <c r="L22" s="66"/>
-      <c r="M22" s="66"/>
-      <c r="N22" s="66"/>
-      <c r="O22" s="66"/>
-      <c r="P22" s="66"/>
-      <c r="Q22" s="66"/>
-      <c r="R22" s="66"/>
-      <c r="S22" s="66"/>
-      <c r="T22" s="66"/>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A23" s="77"/>
-      <c r="B23" s="78"/>
-      <c r="C23" s="82"/>
-      <c r="D23" s="80"/>
-      <c r="E23" s="83"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="65"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="66"/>
-      <c r="K23" s="66"/>
-      <c r="L23" s="66"/>
-      <c r="M23" s="66"/>
-      <c r="N23" s="66"/>
-      <c r="O23" s="66"/>
-      <c r="P23" s="66"/>
-      <c r="Q23" s="66"/>
-      <c r="R23" s="66"/>
-      <c r="S23" s="66"/>
-      <c r="T23" s="66"/>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A24" s="77"/>
-      <c r="B24" s="78" t="s">
-        <v>125</v>
-      </c>
-      <c r="C24" s="82"/>
-      <c r="D24" s="80"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="65"/>
-      <c r="G24" s="65"/>
-      <c r="H24" s="65"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="66"/>
-      <c r="K24" s="66"/>
-      <c r="L24" s="66"/>
-      <c r="M24" s="66"/>
-      <c r="N24" s="66"/>
-      <c r="O24" s="66"/>
-      <c r="P24" s="66"/>
-      <c r="Q24" s="66"/>
-      <c r="R24" s="66"/>
-      <c r="S24" s="66"/>
-      <c r="T24" s="66"/>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A25" s="77"/>
-      <c r="B25" s="78"/>
-      <c r="C25" s="82"/>
-      <c r="D25" s="80"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="65"/>
-      <c r="G25" s="65"/>
-      <c r="H25" s="65"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="66"/>
-      <c r="K25" s="66"/>
-      <c r="L25" s="66"/>
-      <c r="M25" s="66"/>
-      <c r="N25" s="66"/>
-      <c r="O25" s="66"/>
-      <c r="P25" s="66"/>
-      <c r="Q25" s="66"/>
-      <c r="R25" s="66"/>
-      <c r="S25" s="66"/>
-      <c r="T25" s="66"/>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A26" s="77"/>
-      <c r="B26" s="84"/>
-      <c r="C26" s="85"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="87"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="65"/>
-      <c r="H26" s="65"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="66"/>
-      <c r="K26" s="66"/>
-      <c r="L26" s="66"/>
-      <c r="M26" s="66"/>
-      <c r="N26" s="66"/>
-      <c r="O26" s="66"/>
-      <c r="P26" s="66"/>
-      <c r="Q26" s="66"/>
-      <c r="R26" s="66"/>
-      <c r="S26" s="66"/>
-      <c r="T26" s="66"/>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A27" s="72" t="s">
-        <v>109</v>
-      </c>
-      <c r="B27" s="88" t="s">
-        <v>56</v>
-      </c>
-      <c r="C27" s="88"/>
-      <c r="D27" s="88"/>
-      <c r="E27" s="89"/>
-      <c r="F27" s="90" t="s">
-        <v>57</v>
-      </c>
-      <c r="G27" s="90" t="s">
-        <v>57</v>
-      </c>
-      <c r="H27" s="90" t="s">
-        <v>57</v>
-      </c>
-      <c r="I27" s="1"/>
-      <c r="J27" s="91"/>
-      <c r="K27" s="91"/>
-      <c r="L27" s="91"/>
-      <c r="M27" s="91"/>
-      <c r="N27" s="91"/>
-      <c r="O27" s="91"/>
-      <c r="P27" s="91"/>
-      <c r="Q27" s="91"/>
-      <c r="R27" s="91"/>
-      <c r="S27" s="91"/>
-      <c r="T27" s="91"/>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A28" s="77"/>
-      <c r="B28" s="92" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" s="92"/>
-      <c r="D28" s="92"/>
-      <c r="E28" s="93"/>
-      <c r="F28" s="94" t="s">
-        <v>61</v>
-      </c>
-      <c r="G28" s="94" t="s">
-        <v>60</v>
-      </c>
-      <c r="H28" s="94" t="s">
-        <v>60</v>
-      </c>
-      <c r="I28" s="1"/>
-      <c r="J28" s="91"/>
-      <c r="K28" s="91"/>
-      <c r="L28" s="91"/>
-      <c r="M28" s="91"/>
-      <c r="N28" s="91"/>
-      <c r="O28" s="91"/>
-      <c r="P28" s="91"/>
-      <c r="Q28" s="91"/>
-      <c r="R28" s="91"/>
-      <c r="S28" s="91"/>
-      <c r="T28" s="91"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A29" s="77"/>
-      <c r="B29" s="92" t="s">
-        <v>62</v>
-      </c>
-      <c r="C29" s="92"/>
-      <c r="D29" s="92"/>
-      <c r="E29" s="95"/>
-      <c r="F29" s="96" t="s">
+      <c r="D24" s="3"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:19">
+      <c r="B25" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G29" s="96" t="s">
-        <v>63</v>
-      </c>
-      <c r="H29" s="96" t="s">
-        <v>63</v>
-      </c>
-      <c r="I29" s="1"/>
-      <c r="J29" s="97"/>
-      <c r="K29" s="97"/>
-      <c r="L29" s="97"/>
-      <c r="M29" s="97"/>
-      <c r="N29" s="97"/>
-      <c r="O29" s="97"/>
-      <c r="P29" s="97"/>
-      <c r="Q29" s="97"/>
-      <c r="R29" s="97"/>
-      <c r="S29" s="97"/>
-      <c r="T29" s="97"/>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="1:20">
-      <c r="A30" s="98"/>
-      <c r="B30" s="99" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" s="99"/>
-      <c r="D30" s="99"/>
-      <c r="E30" s="100"/>
-      <c r="F30" s="101"/>
-      <c r="G30" s="101">
-        <v>1</v>
-      </c>
-      <c r="H30" s="101">
-        <v>2</v>
-      </c>
-      <c r="I30" s="1"/>
-      <c r="J30" s="102"/>
-      <c r="K30" s="102"/>
-      <c r="L30" s="102"/>
-      <c r="M30" s="102"/>
-      <c r="N30" s="102"/>
-      <c r="O30" s="102"/>
-      <c r="P30" s="102"/>
-      <c r="Q30" s="102"/>
-      <c r="R30" s="102"/>
-      <c r="S30" s="102"/>
-      <c r="T30" s="102"/>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="13.95" spans="1:20">
-      <c r="A31" s="2"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="3"/>
-    </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="2:4">
-      <c r="B33" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D33" s="3"/>
-    </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="2:4">
-      <c r="B34" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C34" s="103">
+      <c r="C25" s="97">
         <v>46063</v>
       </c>
-      <c r="D34" s="3"/>
-    </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="2:4">
-      <c r="B35" s="2">
-        <v>1</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D35" s="3"/>
-    </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="2:4">
-      <c r="B36" s="2">
-        <v>2</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D36" s="3"/>
+      <c r="D25" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="27">
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:K2"/>
-    <mergeCell ref="L2:T2"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:S2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="C3:E3"/>
-    <mergeCell ref="F3:K3"/>
-    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:M3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="F4:K4"/>
-    <mergeCell ref="L4:T4"/>
+    <mergeCell ref="F4:J4"/>
+    <mergeCell ref="K4:S4"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:T5"/>
+    <mergeCell ref="C5:S5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:E6"/>
-    <mergeCell ref="F6:K6"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="O6:T6"/>
+    <mergeCell ref="F6:J6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:S6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C7:E7"/>
-    <mergeCell ref="F7:K7"/>
-    <mergeCell ref="O7:T7"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F7:J7"/>
+    <mergeCell ref="N7:S7"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F27:H27 J27:T27">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F13:G13 I13:S13 I14:S15 I16:S17 F14:G15 F16:G17 F10:G12 I10:S12">
+      <formula1>"O, "</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F18:G18 I18:S18">
       <formula1>"N,A,B, "</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F28:H28 J28:T28">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19:G19 I19:S19">
       <formula1>"P,F, "</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:H13 J14:T26 J10:T13 F14:H26">
-      <formula1>"O, "</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
